--- a/code_book/Libro de codigos redcap.xlsx
+++ b/code_book/Libro de codigos redcap.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C636"/>
+  <dimension ref="A1:C661"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4186,72 +4186,72 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>datohis07_v2___5</t>
+          <t>datohis07_v2___10</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>datohis08_v2</t>
-        </is>
-      </c>
-      <c r="B260" t="inlineStr"/>
+          <t>datohis07_v2</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>datohis08_v2</t>
+          <t>datohis07_v2___11</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>datohis091_v2</t>
-        </is>
-      </c>
-      <c r="B261" t="inlineStr"/>
+          <t>datohis07_v2</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>datohis091_v2</t>
+          <t>datohis07_v2___5</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>datohis092_v2</t>
-        </is>
-      </c>
-      <c r="B262" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>datohis08_v2</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr"/>
       <c r="C262" t="inlineStr">
         <is>
-          <t>datohis092_v2___1</t>
+          <t>datohis08_v2</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>datohis092_v2</t>
-        </is>
-      </c>
-      <c r="B263" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>datohis091_v2</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr"/>
       <c r="C263" t="inlineStr">
         <is>
-          <t>datohis092_v2___2</t>
+          <t>datohis091_v2</t>
         </is>
       </c>
     </row>
@@ -4263,12 +4263,12 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>datohis092_v2___3</t>
+          <t>datohis092_v2___1</t>
         </is>
       </c>
     </row>
@@ -4280,12 +4280,12 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>datohis092_v2___4</t>
+          <t>datohis092_v2___2</t>
         </is>
       </c>
     </row>
@@ -4297,46 +4297,46 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>datohis092_v2___5</t>
+          <t>datohis092_v2___3</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>datohis093_v2</t>
+          <t>datohis092_v2</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>datohis093_v2___1</t>
+          <t>datohis092_v2___4</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>datohis093_v2</t>
+          <t>datohis092_v2</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>datohis093_v2___2</t>
+          <t>datohis092_v2___5</t>
         </is>
       </c>
     </row>
@@ -4348,12 +4348,12 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>datohis093_v2___3</t>
+          <t>datohis093_v2___1</t>
         </is>
       </c>
     </row>
@@ -4365,12 +4365,12 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>datohis093_v2___4</t>
+          <t>datohis093_v2___2</t>
         </is>
       </c>
     </row>
@@ -4382,12 +4382,12 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>datohis093_v2___5</t>
+          <t>datohis093_v2___3</t>
         </is>
       </c>
     </row>
@@ -4399,46 +4399,46 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>datohis093_v2___6</t>
+          <t>datohis093_v2___4</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>datohis094_v2</t>
+          <t>datohis093_v2</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>datohis094_v2___1</t>
+          <t>datohis093_v2___5</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>datohis094_v2</t>
+          <t>datohis093_v2</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>datohis094_v2___2</t>
+          <t>datohis093_v2___6</t>
         </is>
       </c>
     </row>
@@ -4450,12 +4450,12 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>datohis094_v2___3</t>
+          <t>datohis094_v2___1</t>
         </is>
       </c>
     </row>
@@ -4467,12 +4467,12 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>datohis094_v2___4</t>
+          <t>datohis094_v2___2</t>
         </is>
       </c>
     </row>
@@ -4484,12 +4484,12 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>datohis094_v2___5</t>
+          <t>datohis094_v2___3</t>
         </is>
       </c>
     </row>
@@ -4501,124 +4501,124 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>datohis094_v2___6</t>
+          <t>datohis094_v2___4</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>datohis095_v2</t>
-        </is>
-      </c>
-      <c r="B279" t="inlineStr"/>
+          <t>datohis094_v2</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>datohis095_v2</t>
+          <t>datohis094_v2___5</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>datohis0915_v2</t>
-        </is>
-      </c>
-      <c r="B280" t="inlineStr"/>
+          <t>datohis094_v2</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>datohis0915_v2</t>
+          <t>datohis094_v2___6</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>datohis0925_v2</t>
+          <t>datohis095_v2</t>
         </is>
       </c>
       <c r="B281" t="inlineStr"/>
       <c r="C281" t="inlineStr">
         <is>
-          <t>datohis0925_v2</t>
+          <t>datohis095_v2</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>datohis0935_v2</t>
+          <t>datohis0915_v2</t>
         </is>
       </c>
       <c r="B282" t="inlineStr"/>
       <c r="C282" t="inlineStr">
         <is>
-          <t>datohis0935_v2</t>
+          <t>datohis0915_v2</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>datohis0945_v2</t>
+          <t>datohis0925_v2</t>
         </is>
       </c>
       <c r="B283" t="inlineStr"/>
       <c r="C283" t="inlineStr">
         <is>
-          <t>datohis0945_v2</t>
+          <t>datohis0925_v2</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>datohis0955_v2</t>
+          <t>datohis0935_v2</t>
         </is>
       </c>
       <c r="B284" t="inlineStr"/>
       <c r="C284" t="inlineStr">
         <is>
-          <t>datohis0955_v2</t>
+          <t>datohis0935_v2</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>datohis10_v2</t>
-        </is>
-      </c>
-      <c r="B285" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>datohis0945_v2</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr"/>
       <c r="C285" t="inlineStr">
         <is>
-          <t>datohis10_v2___1</t>
+          <t>datohis0945_v2</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>datohis10_v2</t>
-        </is>
-      </c>
-      <c r="B286" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>datohis0955_v2</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr"/>
       <c r="C286" t="inlineStr">
         <is>
-          <t>datohis10_v2___2</t>
+          <t>datohis0955_v2</t>
         </is>
       </c>
     </row>
@@ -4630,12 +4630,12 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>datohis10_v2___3</t>
+          <t>datohis10_v2___1</t>
         </is>
       </c>
     </row>
@@ -4647,12 +4647,12 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>datohis10_v2___4</t>
+          <t>datohis10_v2___2</t>
         </is>
       </c>
     </row>
@@ -4664,12 +4664,12 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>datohis10_v2___5</t>
+          <t>datohis10_v2___3</t>
         </is>
       </c>
     </row>
@@ -4681,85 +4681,85 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>datohis10_v2___6</t>
+          <t>datohis10_v2___4</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>datohis10_v2new</t>
-        </is>
-      </c>
-      <c r="B291" t="inlineStr"/>
+          <t>datohis10_v2</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>datohis10_v2new</t>
+          <t>datohis10_v2___5</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>datohis11_v2f</t>
-        </is>
-      </c>
-      <c r="B292" t="inlineStr"/>
+          <t>datohis10_v2</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>datohis11_v2f</t>
+          <t>datohis10_v2___6</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>datohis11_v2</t>
+          <t>datohis10_v2new</t>
         </is>
       </c>
       <c r="B293" t="inlineStr"/>
       <c r="C293" t="inlineStr">
         <is>
-          <t>datohis11_v2</t>
+          <t>datohis10_v2new</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>datohis131_v2</t>
-        </is>
-      </c>
-      <c r="B294" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>datohis11_v2f</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr"/>
       <c r="C294" t="inlineStr">
         <is>
-          <t>datohis131_v2___1</t>
+          <t>datohis11_v2f</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>datohis131_v2</t>
-        </is>
-      </c>
-      <c r="B295" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>datohis11_v2</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr"/>
       <c r="C295" t="inlineStr">
         <is>
-          <t>datohis131_v2___2</t>
+          <t>datohis11_v2</t>
         </is>
       </c>
     </row>
@@ -4771,46 +4771,46 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>datohis131_v2___0</t>
+          <t>datohis131_v2___1</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>datohis132_v2</t>
+          <t>datohis131_v2</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>datohis132_v2___1</t>
+          <t>datohis131_v2___2</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>datohis132_v2</t>
+          <t>datohis131_v2</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>datohis132_v2___2</t>
+          <t>datohis131_v2___0</t>
         </is>
       </c>
     </row>
@@ -4822,3044 +4822,3044 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>datohis132_v2___0</t>
+          <t>datohis132_v2___1</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>datohis131a_v2</t>
-        </is>
-      </c>
-      <c r="B300" t="inlineStr"/>
+          <t>datohis132_v2</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>datohis131a_v2</t>
+          <t>datohis132_v2___2</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>datohis132a_v2</t>
-        </is>
-      </c>
-      <c r="B301" t="inlineStr"/>
+          <t>datohis132_v2</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>datohis132a_v2</t>
+          <t>datohis132_v2___0</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>datohis131b_v2</t>
+          <t>datohis131a_v2</t>
         </is>
       </c>
       <c r="B302" t="inlineStr"/>
       <c r="C302" t="inlineStr">
         <is>
-          <t>datohis131b_v2</t>
+          <t>datohis131a_v2</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>datohis132b_v2</t>
+          <t>datohis132a_v2</t>
         </is>
       </c>
       <c r="B303" t="inlineStr"/>
       <c r="C303" t="inlineStr">
         <is>
-          <t>datohis132b_v2</t>
+          <t>datohis132a_v2</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>datohis131c_v2</t>
+          <t>datohis131b_v2</t>
         </is>
       </c>
       <c r="B304" t="inlineStr"/>
       <c r="C304" t="inlineStr">
         <is>
-          <t>datohis131c_v2</t>
+          <t>datohis131b_v2</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>datohis132c_v2</t>
+          <t>datohis132b_v2</t>
         </is>
       </c>
       <c r="B305" t="inlineStr"/>
       <c r="C305" t="inlineStr">
         <is>
-          <t>datohis132c_v2</t>
+          <t>datohis132b_v2</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>datohis131d_v2</t>
+          <t>datohis131c_v2</t>
         </is>
       </c>
       <c r="B306" t="inlineStr"/>
       <c r="C306" t="inlineStr">
         <is>
-          <t>datohis131d_v2</t>
+          <t>datohis131c_v2</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>datohis132d_v2</t>
+          <t>datohis132c_v2</t>
         </is>
       </c>
       <c r="B307" t="inlineStr"/>
       <c r="C307" t="inlineStr">
         <is>
-          <t>datohis132d_v2</t>
+          <t>datohis132c_v2</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>datohis14_v2f</t>
+          <t>datohis131d_v2</t>
         </is>
       </c>
       <c r="B308" t="inlineStr"/>
       <c r="C308" t="inlineStr">
         <is>
-          <t>datohis14_v2f</t>
+          <t>datohis131d_v2</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>datohis14_v2</t>
+          <t>datohis132d_v2</t>
         </is>
       </c>
       <c r="B309" t="inlineStr"/>
       <c r="C309" t="inlineStr">
         <is>
-          <t>datohis14_v2</t>
+          <t>datohis132d_v2</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>datohis141_v2</t>
+          <t>datohis14_v2f</t>
         </is>
       </c>
       <c r="B310" t="inlineStr"/>
       <c r="C310" t="inlineStr">
         <is>
-          <t>datohis141_v2</t>
+          <t>datohis14_v2f</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>datohis142_v2</t>
+          <t>datohis14_v2</t>
         </is>
       </c>
       <c r="B311" t="inlineStr"/>
       <c r="C311" t="inlineStr">
         <is>
-          <t>datohis142_v2</t>
+          <t>datohis14_v2</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>datohis15_v2s</t>
+          <t>datohis141_v2</t>
         </is>
       </c>
       <c r="B312" t="inlineStr"/>
       <c r="C312" t="inlineStr">
         <is>
-          <t>datohis15_v2s</t>
+          <t>datohis141_v2</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>datohis15_v2f</t>
+          <t>datohis142_v2</t>
         </is>
       </c>
       <c r="B313" t="inlineStr"/>
       <c r="C313" t="inlineStr">
         <is>
-          <t>datohis15_v2f</t>
+          <t>datohis142_v2</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>datohis15_v2</t>
+          <t>datohis15_v2s</t>
         </is>
       </c>
       <c r="B314" t="inlineStr"/>
       <c r="C314" t="inlineStr">
         <is>
-          <t>datohis15_v2</t>
+          <t>datohis15_v2s</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>datohis153_v2</t>
+          <t>datohis15_v2f</t>
         </is>
       </c>
       <c r="B315" t="inlineStr"/>
       <c r="C315" t="inlineStr">
         <is>
-          <t>datohis153_v2</t>
+          <t>datohis15_v2f</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>datohis16_v2</t>
+          <t>datohis15_v2</t>
         </is>
       </c>
       <c r="B316" t="inlineStr"/>
       <c r="C316" t="inlineStr">
         <is>
-          <t>datohis16_v2</t>
+          <t>datohis15_v2</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>datohis16a_v2</t>
+          <t>datohis153_v2</t>
         </is>
       </c>
       <c r="B317" t="inlineStr"/>
       <c r="C317" t="inlineStr">
         <is>
-          <t>datohis16a_v2</t>
+          <t>datohis153_v2</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>datohis164_v2</t>
+          <t>datohis16_v2</t>
         </is>
       </c>
       <c r="B318" t="inlineStr"/>
       <c r="C318" t="inlineStr">
         <is>
-          <t>datohis164_v2</t>
+          <t>datohis16_v2</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>datohis17_v2</t>
+          <t>datohis16a_v2</t>
         </is>
       </c>
       <c r="B319" t="inlineStr"/>
       <c r="C319" t="inlineStr">
         <is>
-          <t>datohis17_v2</t>
+          <t>datohis16a_v2</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>datohis171_v2</t>
+          <t>datohis164_v2</t>
         </is>
       </c>
       <c r="B320" t="inlineStr"/>
       <c r="C320" t="inlineStr">
         <is>
-          <t>datohis171_v2</t>
+          <t>datohis164_v2</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>datohis18_v2</t>
+          <t>datohis17_v2</t>
         </is>
       </c>
       <c r="B321" t="inlineStr"/>
       <c r="C321" t="inlineStr">
         <is>
-          <t>datohis18_v2</t>
+          <t>datohis17_v2</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>datohis19_v2</t>
+          <t>datohis171_v2</t>
         </is>
       </c>
       <c r="B322" t="inlineStr"/>
       <c r="C322" t="inlineStr">
         <is>
-          <t>datohis19_v2</t>
+          <t>datohis171_v2</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>datohis20_v2</t>
+          <t>datohis18_v2</t>
         </is>
       </c>
       <c r="B323" t="inlineStr"/>
       <c r="C323" t="inlineStr">
         <is>
-          <t>datohis20_v2</t>
+          <t>datohis18_v2</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>datohis201_v2</t>
+          <t>datohis19_v2</t>
         </is>
       </c>
       <c r="B324" t="inlineStr"/>
       <c r="C324" t="inlineStr">
         <is>
-          <t>datohis201_v2</t>
+          <t>datohis19_v2</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>datohis22_v2</t>
+          <t>datohis20_v2</t>
         </is>
       </c>
       <c r="B325" t="inlineStr"/>
       <c r="C325" t="inlineStr">
         <is>
-          <t>datohis22_v2</t>
+          <t>datohis20_v2</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>datohi23_v2</t>
+          <t>datohis201_v2</t>
         </is>
       </c>
       <c r="B326" t="inlineStr"/>
       <c r="C326" t="inlineStr">
         <is>
-          <t>datohi23_v2</t>
+          <t>datohis201_v2</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>calculoeta</t>
+          <t>datohis22_v2</t>
         </is>
       </c>
       <c r="B327" t="inlineStr"/>
       <c r="C327" t="inlineStr">
         <is>
-          <t>calculoeta</t>
+          <t>datohis22_v2</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>calculoetac</t>
+          <t>datohi23_v2</t>
         </is>
       </c>
       <c r="B328" t="inlineStr"/>
       <c r="C328" t="inlineStr">
         <is>
-          <t>calculoetac</t>
+          <t>datohi23_v2</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>calculoconint</t>
+          <t>calculoeta</t>
         </is>
       </c>
       <c r="B329" t="inlineStr"/>
       <c r="C329" t="inlineStr">
         <is>
-          <t>calculoconint</t>
+          <t>calculoeta</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>datohis21a_v2</t>
+          <t>calculoetac</t>
         </is>
       </c>
       <c r="B330" t="inlineStr"/>
       <c r="C330" t="inlineStr">
         <is>
-          <t>datohis21a_v2</t>
+          <t>calculoetac</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>datohis21a1c_v2</t>
+          <t>calculoconint</t>
         </is>
       </c>
       <c r="B331" t="inlineStr"/>
       <c r="C331" t="inlineStr">
         <is>
-          <t>datohis21a1c_v2</t>
+          <t>calculoconint</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>datohis21a2c_v2</t>
+          <t>datohis21a_v2</t>
         </is>
       </c>
       <c r="B332" t="inlineStr"/>
       <c r="C332" t="inlineStr">
         <is>
-          <t>datohis21a2c_v2</t>
+          <t>datohis21a_v2</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>datohis21a3c_v2</t>
+          <t>datohis21a1c_v2</t>
         </is>
       </c>
       <c r="B333" t="inlineStr"/>
       <c r="C333" t="inlineStr">
         <is>
-          <t>datohis21a3c_v2</t>
+          <t>datohis21a1c_v2</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>datohis21b_v2</t>
+          <t>datohis21a2c_v2</t>
         </is>
       </c>
       <c r="B334" t="inlineStr"/>
       <c r="C334" t="inlineStr">
         <is>
-          <t>datohis21b_v2</t>
+          <t>datohis21a2c_v2</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>datohis21b1c_v2</t>
+          <t>datohis21a3c_v2</t>
         </is>
       </c>
       <c r="B335" t="inlineStr"/>
       <c r="C335" t="inlineStr">
         <is>
-          <t>datohis21b1c_v2</t>
+          <t>datohis21a3c_v2</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>datohis21c_v2</t>
+          <t>datohis21b_v2</t>
         </is>
       </c>
       <c r="B336" t="inlineStr"/>
       <c r="C336" t="inlineStr">
         <is>
-          <t>datohis21c_v2</t>
+          <t>datohis21b_v2</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>datohis21cc_v2</t>
+          <t>datohis21b1c_v2</t>
         </is>
       </c>
       <c r="B337" t="inlineStr"/>
       <c r="C337" t="inlineStr">
         <is>
-          <t>datohis21cc_v2</t>
+          <t>datohis21b1c_v2</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>exclusion2a</t>
+          <t>datohis21c_v2</t>
         </is>
       </c>
       <c r="B338" t="inlineStr"/>
       <c r="C338" t="inlineStr">
         <is>
-          <t>exclusion2a</t>
+          <t>datohis21c_v2</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>formulario_2a_post_tiroidectomia_complete</t>
+          <t>datohis21cc_v2</t>
         </is>
       </c>
       <c r="B339" t="inlineStr"/>
       <c r="C339" t="inlineStr">
         <is>
-          <t>formulario_2a_post_tiroidectomia_complete</t>
+          <t>datohis21cc_v2</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>f2b_fecha_de_visita</t>
+          <t>exclusion2a</t>
         </is>
       </c>
       <c r="B340" t="inlineStr"/>
       <c r="C340" t="inlineStr">
         <is>
-          <t>f2b_fecha_de_visita</t>
+          <t>exclusion2a</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>f2bp001</t>
+          <t>formulario_2a_post_tiroidectomia_complete</t>
         </is>
       </c>
       <c r="B341" t="inlineStr"/>
       <c r="C341" t="inlineStr">
         <is>
-          <t>f2bp001</t>
+          <t>formulario_2a_post_tiroidectomia_complete</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>f2bp002</t>
+          <t>f2b_fecha_de_visita</t>
         </is>
       </c>
       <c r="B342" t="inlineStr"/>
       <c r="C342" t="inlineStr">
         <is>
-          <t>f2bp002</t>
+          <t>f2b_fecha_de_visita</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>f2bp003</t>
+          <t>f2bp001</t>
         </is>
       </c>
       <c r="B343" t="inlineStr"/>
       <c r="C343" t="inlineStr">
         <is>
-          <t>f2bp003</t>
+          <t>f2bp001</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>f2b9004</t>
+          <t>f2bp002</t>
         </is>
       </c>
       <c r="B344" t="inlineStr"/>
       <c r="C344" t="inlineStr">
         <is>
-          <t>f2b9004</t>
+          <t>f2bp002</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>f2bp005</t>
+          <t>f2bp003</t>
         </is>
       </c>
       <c r="B345" t="inlineStr"/>
       <c r="C345" t="inlineStr">
         <is>
-          <t>f2bp005</t>
+          <t>f2bp003</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>f2bp006</t>
+          <t>f2b9004</t>
         </is>
       </c>
       <c r="B346" t="inlineStr"/>
       <c r="C346" t="inlineStr">
         <is>
-          <t>f2bp006</t>
+          <t>f2b9004</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>f2bp006a</t>
+          <t>f2bp005</t>
         </is>
       </c>
       <c r="B347" t="inlineStr"/>
       <c r="C347" t="inlineStr">
         <is>
-          <t>f2bp006a</t>
+          <t>f2bp005</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>f2bp007</t>
+          <t>f2bp006</t>
         </is>
       </c>
       <c r="B348" t="inlineStr"/>
       <c r="C348" t="inlineStr">
         <is>
-          <t>f2bp007</t>
+          <t>f2bp006</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>f2bp008</t>
+          <t>f2bp006a</t>
         </is>
       </c>
       <c r="B349" t="inlineStr"/>
       <c r="C349" t="inlineStr">
         <is>
-          <t>f2bp008</t>
+          <t>f2bp006a</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>f2bp009a</t>
+          <t>f2bp007</t>
         </is>
       </c>
       <c r="B350" t="inlineStr"/>
       <c r="C350" t="inlineStr">
         <is>
-          <t>f2bp009a</t>
+          <t>f2bp007</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>f2bp009b</t>
+          <t>f2bp008</t>
         </is>
       </c>
       <c r="B351" t="inlineStr"/>
       <c r="C351" t="inlineStr">
         <is>
-          <t>f2bp009b</t>
+          <t>f2bp008</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>f2b9010a</t>
+          <t>f2bp009a</t>
         </is>
       </c>
       <c r="B352" t="inlineStr"/>
       <c r="C352" t="inlineStr">
         <is>
-          <t>f2b9010a</t>
+          <t>f2bp009a</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>f2bp010b</t>
+          <t>f2bp009b</t>
         </is>
       </c>
       <c r="B353" t="inlineStr"/>
       <c r="C353" t="inlineStr">
         <is>
-          <t>f2bp010b</t>
+          <t>f2bp009b</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>f2bp011a</t>
+          <t>f2b9010a</t>
         </is>
       </c>
       <c r="B354" t="inlineStr"/>
       <c r="C354" t="inlineStr">
         <is>
-          <t>f2bp011a</t>
+          <t>f2b9010a</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>f2bp011b</t>
+          <t>f2bp010b</t>
         </is>
       </c>
       <c r="B355" t="inlineStr"/>
       <c r="C355" t="inlineStr">
         <is>
-          <t>f2bp011b</t>
+          <t>f2bp010b</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>f2bp012</t>
+          <t>f2bp011a</t>
         </is>
       </c>
       <c r="B356" t="inlineStr"/>
       <c r="C356" t="inlineStr">
         <is>
-          <t>f2bp012</t>
+          <t>f2bp011a</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>f2bp013</t>
+          <t>f2bp011b</t>
         </is>
       </c>
       <c r="B357" t="inlineStr"/>
       <c r="C357" t="inlineStr">
         <is>
-          <t>f2bp013</t>
+          <t>f2bp011b</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>f2b9014</t>
+          <t>f2bp012</t>
         </is>
       </c>
       <c r="B358" t="inlineStr"/>
       <c r="C358" t="inlineStr">
         <is>
-          <t>f2b9014</t>
+          <t>f2bp012</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>f2b9015</t>
+          <t>f2bp013</t>
         </is>
       </c>
       <c r="B359" t="inlineStr"/>
       <c r="C359" t="inlineStr">
         <is>
-          <t>f2b9015</t>
+          <t>f2bp013</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>f2btq001</t>
+          <t>f2b9014</t>
         </is>
       </c>
       <c r="B360" t="inlineStr"/>
       <c r="C360" t="inlineStr">
         <is>
-          <t>f2btq001</t>
+          <t>f2b9014</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>f2btq002</t>
+          <t>f2b9015</t>
         </is>
       </c>
       <c r="B361" t="inlineStr"/>
       <c r="C361" t="inlineStr">
         <is>
-          <t>f2btq002</t>
+          <t>f2b9015</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>f2btq003</t>
+          <t>f2btq001</t>
         </is>
       </c>
       <c r="B362" t="inlineStr"/>
       <c r="C362" t="inlineStr">
         <is>
-          <t>f2btq003</t>
+          <t>f2btq001</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>f2btq004</t>
+          <t>f2btq002</t>
         </is>
       </c>
       <c r="B363" t="inlineStr"/>
       <c r="C363" t="inlineStr">
         <is>
-          <t>f2btq004</t>
+          <t>f2btq002</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>f2btq005</t>
+          <t>f2btq003</t>
         </is>
       </c>
       <c r="B364" t="inlineStr"/>
       <c r="C364" t="inlineStr">
         <is>
-          <t>f2btq005</t>
+          <t>f2btq003</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>f2btq007</t>
+          <t>f2btq004</t>
         </is>
       </c>
       <c r="B365" t="inlineStr"/>
       <c r="C365" t="inlineStr">
         <is>
-          <t>f2btq007</t>
+          <t>f2btq004</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>f2btq008</t>
+          <t>f2btq005</t>
         </is>
       </c>
       <c r="B366" t="inlineStr"/>
       <c r="C366" t="inlineStr">
         <is>
-          <t>f2btq008</t>
+          <t>f2btq005</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>f2btq009</t>
+          <t>f2btq007</t>
         </is>
       </c>
       <c r="B367" t="inlineStr"/>
       <c r="C367" t="inlineStr">
         <is>
-          <t>f2btq009</t>
+          <t>f2btq007</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>f2btq010</t>
+          <t>f2btq008</t>
         </is>
       </c>
       <c r="B368" t="inlineStr"/>
       <c r="C368" t="inlineStr">
         <is>
-          <t>f2btq010</t>
+          <t>f2btq008</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>f2btq011</t>
+          <t>f2btq009</t>
         </is>
       </c>
       <c r="B369" t="inlineStr"/>
       <c r="C369" t="inlineStr">
         <is>
-          <t>f2btq011</t>
+          <t>f2btq009</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>f2btq012</t>
+          <t>f2btq010</t>
         </is>
       </c>
       <c r="B370" t="inlineStr"/>
       <c r="C370" t="inlineStr">
         <is>
-          <t>f2btq012</t>
+          <t>f2btq010</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>f2btq013</t>
+          <t>f2btq011</t>
         </is>
       </c>
       <c r="B371" t="inlineStr"/>
       <c r="C371" t="inlineStr">
         <is>
-          <t>f2btq013</t>
+          <t>f2btq011</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>f2btq014</t>
+          <t>f2btq012</t>
         </is>
       </c>
       <c r="B372" t="inlineStr"/>
       <c r="C372" t="inlineStr">
         <is>
-          <t>f2btq014</t>
+          <t>f2btq012</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>f2btq015</t>
+          <t>f2btq013</t>
         </is>
       </c>
       <c r="B373" t="inlineStr"/>
       <c r="C373" t="inlineStr">
         <is>
-          <t>f2btq015</t>
+          <t>f2btq013</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>f2btq016</t>
+          <t>f2btq014</t>
         </is>
       </c>
       <c r="B374" t="inlineStr"/>
       <c r="C374" t="inlineStr">
         <is>
-          <t>f2btq016</t>
+          <t>f2btq014</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>f2btq017</t>
+          <t>f2btq015</t>
         </is>
       </c>
       <c r="B375" t="inlineStr"/>
       <c r="C375" t="inlineStr">
         <is>
-          <t>f2btq017</t>
+          <t>f2btq015</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>f2btq018</t>
+          <t>f2btq016</t>
         </is>
       </c>
       <c r="B376" t="inlineStr"/>
       <c r="C376" t="inlineStr">
         <is>
-          <t>f2btq018</t>
+          <t>f2btq016</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>f2btq019</t>
+          <t>f2btq017</t>
         </is>
       </c>
       <c r="B377" t="inlineStr"/>
       <c r="C377" t="inlineStr">
         <is>
-          <t>f2btq019</t>
+          <t>f2btq017</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>f2btq020</t>
+          <t>f2btq018</t>
         </is>
       </c>
       <c r="B378" t="inlineStr"/>
       <c r="C378" t="inlineStr">
         <is>
-          <t>f2btq020</t>
+          <t>f2btq018</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>f2btq021</t>
+          <t>f2btq019</t>
         </is>
       </c>
       <c r="B379" t="inlineStr"/>
       <c r="C379" t="inlineStr">
         <is>
-          <t>f2btq021</t>
+          <t>f2btq019</t>
         </is>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>f2btq022</t>
+          <t>f2btq020</t>
         </is>
       </c>
       <c r="B380" t="inlineStr"/>
       <c r="C380" t="inlineStr">
         <is>
-          <t>f2btq022</t>
+          <t>f2btq020</t>
         </is>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>f2btq023</t>
+          <t>f2btq021</t>
         </is>
       </c>
       <c r="B381" t="inlineStr"/>
       <c r="C381" t="inlineStr">
         <is>
-          <t>f2btq023</t>
+          <t>f2btq021</t>
         </is>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>f2btq024</t>
+          <t>f2btq022</t>
         </is>
       </c>
       <c r="B382" t="inlineStr"/>
       <c r="C382" t="inlineStr">
         <is>
-          <t>f2btq024</t>
+          <t>f2btq022</t>
         </is>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>formulario_2b_complete</t>
+          <t>f2btq023</t>
         </is>
       </c>
       <c r="B383" t="inlineStr"/>
       <c r="C383" t="inlineStr">
         <is>
-          <t>formulario_2b_complete</t>
+          <t>f2btq023</t>
         </is>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>f2c_fecha_de_visita</t>
+          <t>f2btq024</t>
         </is>
       </c>
       <c r="B384" t="inlineStr"/>
       <c r="C384" t="inlineStr">
         <is>
-          <t>f2c_fecha_de_visita</t>
+          <t>f2btq024</t>
         </is>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>f2c001</t>
+          <t>formulario_2b_complete</t>
         </is>
       </c>
       <c r="B385" t="inlineStr"/>
       <c r="C385" t="inlineStr">
         <is>
-          <t>f2c001</t>
+          <t>formulario_2b_complete</t>
         </is>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>f2c002</t>
+          <t>f2c_fecha_de_visita</t>
         </is>
       </c>
       <c r="B386" t="inlineStr"/>
       <c r="C386" t="inlineStr">
         <is>
-          <t>f2c002</t>
+          <t>f2c_fecha_de_visita</t>
         </is>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>f2c003</t>
+          <t>f2c001</t>
         </is>
       </c>
       <c r="B387" t="inlineStr"/>
       <c r="C387" t="inlineStr">
         <is>
-          <t>f2c003</t>
+          <t>f2c001</t>
         </is>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>f2c004</t>
+          <t>f2c002</t>
         </is>
       </c>
       <c r="B388" t="inlineStr"/>
       <c r="C388" t="inlineStr">
         <is>
-          <t>f2c004</t>
+          <t>f2c002</t>
         </is>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>f2c004a</t>
+          <t>f2c003</t>
         </is>
       </c>
       <c r="B389" t="inlineStr"/>
       <c r="C389" t="inlineStr">
         <is>
-          <t>f2c004a</t>
+          <t>f2c003</t>
         </is>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>f2c005</t>
+          <t>f2c004</t>
         </is>
       </c>
       <c r="B390" t="inlineStr"/>
       <c r="C390" t="inlineStr">
         <is>
-          <t>f2c005</t>
+          <t>f2c004</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>f2c006</t>
+          <t>f2c004a</t>
         </is>
       </c>
       <c r="B391" t="inlineStr"/>
       <c r="C391" t="inlineStr">
         <is>
-          <t>f2c006</t>
+          <t>f2c004a</t>
         </is>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>f2c007</t>
+          <t>f2c005</t>
         </is>
       </c>
       <c r="B392" t="inlineStr"/>
       <c r="C392" t="inlineStr">
         <is>
-          <t>f2c007</t>
+          <t>f2c005</t>
         </is>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>f2c008</t>
+          <t>f2c006</t>
         </is>
       </c>
       <c r="B393" t="inlineStr"/>
       <c r="C393" t="inlineStr">
         <is>
-          <t>f2c008</t>
+          <t>f2c006</t>
         </is>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>f2c009</t>
+          <t>f2c007</t>
         </is>
       </c>
       <c r="B394" t="inlineStr"/>
       <c r="C394" t="inlineStr">
         <is>
-          <t>f2c009</t>
+          <t>f2c007</t>
         </is>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>f2c010</t>
+          <t>f2c008</t>
         </is>
       </c>
       <c r="B395" t="inlineStr"/>
       <c r="C395" t="inlineStr">
         <is>
-          <t>f2c010</t>
+          <t>f2c008</t>
         </is>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>f2c011</t>
+          <t>f2c009</t>
         </is>
       </c>
       <c r="B396" t="inlineStr"/>
       <c r="C396" t="inlineStr">
         <is>
-          <t>f2c011</t>
+          <t>f2c009</t>
         </is>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>f2c012</t>
+          <t>f2c010</t>
         </is>
       </c>
       <c r="B397" t="inlineStr"/>
       <c r="C397" t="inlineStr">
         <is>
-          <t>f2c012</t>
+          <t>f2c010</t>
         </is>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>f2c013</t>
+          <t>f2c011</t>
         </is>
       </c>
       <c r="B398" t="inlineStr"/>
       <c r="C398" t="inlineStr">
         <is>
-          <t>f2c013</t>
+          <t>f2c011</t>
         </is>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>f2c014</t>
+          <t>f2c012</t>
         </is>
       </c>
       <c r="B399" t="inlineStr"/>
       <c r="C399" t="inlineStr">
         <is>
-          <t>f2c014</t>
+          <t>f2c012</t>
         </is>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>f2c015</t>
+          <t>f2c013</t>
         </is>
       </c>
       <c r="B400" t="inlineStr"/>
       <c r="C400" t="inlineStr">
         <is>
-          <t>f2c015</t>
+          <t>f2c013</t>
         </is>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>f2c016</t>
+          <t>f2c014</t>
         </is>
       </c>
       <c r="B401" t="inlineStr"/>
       <c r="C401" t="inlineStr">
         <is>
-          <t>f2c016</t>
+          <t>f2c014</t>
         </is>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>f2c017</t>
+          <t>f2c015</t>
         </is>
       </c>
       <c r="B402" t="inlineStr"/>
       <c r="C402" t="inlineStr">
         <is>
-          <t>f2c017</t>
+          <t>f2c015</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>f2c018</t>
+          <t>f2c016</t>
         </is>
       </c>
       <c r="B403" t="inlineStr"/>
       <c r="C403" t="inlineStr">
         <is>
-          <t>f2c018</t>
+          <t>f2c016</t>
         </is>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>f2cm001</t>
+          <t>f2c017</t>
         </is>
       </c>
       <c r="B404" t="inlineStr"/>
       <c r="C404" t="inlineStr">
         <is>
-          <t>f2cm001</t>
+          <t>f2c017</t>
         </is>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>f2cm002</t>
+          <t>f2c018</t>
         </is>
       </c>
       <c r="B405" t="inlineStr"/>
       <c r="C405" t="inlineStr">
         <is>
-          <t>f2cm002</t>
+          <t>f2c018</t>
         </is>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>f2cm003</t>
+          <t>f2cm001</t>
         </is>
       </c>
       <c r="B406" t="inlineStr"/>
       <c r="C406" t="inlineStr">
         <is>
-          <t>f2cm003</t>
+          <t>f2cm001</t>
         </is>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>f2cm004</t>
+          <t>f2cm002</t>
         </is>
       </c>
       <c r="B407" t="inlineStr"/>
       <c r="C407" t="inlineStr">
         <is>
-          <t>f2cm004</t>
+          <t>f2cm002</t>
         </is>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>f2cm005</t>
+          <t>f2cm003</t>
         </is>
       </c>
       <c r="B408" t="inlineStr"/>
       <c r="C408" t="inlineStr">
         <is>
-          <t>f2cm005</t>
+          <t>f2cm003</t>
         </is>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>f2cm006</t>
+          <t>f2cm004</t>
         </is>
       </c>
       <c r="B409" t="inlineStr"/>
       <c r="C409" t="inlineStr">
         <is>
-          <t>f2cm006</t>
+          <t>f2cm004</t>
         </is>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>f2cm007</t>
+          <t>f2cm005</t>
         </is>
       </c>
       <c r="B410" t="inlineStr"/>
       <c r="C410" t="inlineStr">
         <is>
-          <t>f2cm007</t>
+          <t>f2cm005</t>
         </is>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>f2cm008</t>
+          <t>f2cm006</t>
         </is>
       </c>
       <c r="B411" t="inlineStr"/>
       <c r="C411" t="inlineStr">
         <is>
-          <t>f2cm008</t>
+          <t>f2cm006</t>
         </is>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>f2cm009</t>
+          <t>f2cm007</t>
         </is>
       </c>
       <c r="B412" t="inlineStr"/>
       <c r="C412" t="inlineStr">
         <is>
-          <t>f2cm009</t>
+          <t>f2cm007</t>
         </is>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>f2cm010</t>
+          <t>f2cm008</t>
         </is>
       </c>
       <c r="B413" t="inlineStr"/>
       <c r="C413" t="inlineStr">
         <is>
-          <t>f2cm010</t>
+          <t>f2cm008</t>
         </is>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>f2cm011</t>
+          <t>f2cm009</t>
         </is>
       </c>
       <c r="B414" t="inlineStr"/>
       <c r="C414" t="inlineStr">
         <is>
-          <t>f2cm011</t>
+          <t>f2cm009</t>
         </is>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>f2cm012</t>
+          <t>f2cm010</t>
         </is>
       </c>
       <c r="B415" t="inlineStr"/>
       <c r="C415" t="inlineStr">
         <is>
-          <t>f2cm012</t>
+          <t>f2cm010</t>
         </is>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>f2c019</t>
+          <t>f2cm011</t>
         </is>
       </c>
       <c r="B416" t="inlineStr"/>
       <c r="C416" t="inlineStr">
         <is>
-          <t>f2c019</t>
+          <t>f2cm011</t>
         </is>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>f2c020</t>
+          <t>f2cm012</t>
         </is>
       </c>
       <c r="B417" t="inlineStr"/>
       <c r="C417" t="inlineStr">
         <is>
-          <t>f2c020</t>
+          <t>f2cm012</t>
         </is>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>f2c021</t>
+          <t>f2c019</t>
         </is>
       </c>
       <c r="B418" t="inlineStr"/>
       <c r="C418" t="inlineStr">
         <is>
-          <t>f2c021</t>
+          <t>f2c019</t>
         </is>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>f2c022</t>
+          <t>f2c020</t>
         </is>
       </c>
       <c r="B419" t="inlineStr"/>
       <c r="C419" t="inlineStr">
         <is>
-          <t>f2c022</t>
+          <t>f2c020</t>
         </is>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>f2c023</t>
+          <t>f2c021</t>
         </is>
       </c>
       <c r="B420" t="inlineStr"/>
       <c r="C420" t="inlineStr">
         <is>
-          <t>f2c023</t>
+          <t>f2c021</t>
         </is>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>f2c024</t>
+          <t>f2c022</t>
         </is>
       </c>
       <c r="B421" t="inlineStr"/>
       <c r="C421" t="inlineStr">
         <is>
-          <t>f2c024</t>
+          <t>f2c022</t>
         </is>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>f2c025</t>
+          <t>f2c023</t>
         </is>
       </c>
       <c r="B422" t="inlineStr"/>
       <c r="C422" t="inlineStr">
         <is>
-          <t>f2c025</t>
+          <t>f2c023</t>
         </is>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>f2ctq001</t>
+          <t>f2c024</t>
         </is>
       </c>
       <c r="B423" t="inlineStr"/>
       <c r="C423" t="inlineStr">
         <is>
-          <t>f2ctq001</t>
+          <t>f2c024</t>
         </is>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>f2ctq002</t>
+          <t>f2c025</t>
         </is>
       </c>
       <c r="B424" t="inlineStr"/>
       <c r="C424" t="inlineStr">
         <is>
-          <t>f2ctq002</t>
+          <t>f2c025</t>
         </is>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>f2ctq003</t>
+          <t>f2ctq001</t>
         </is>
       </c>
       <c r="B425" t="inlineStr"/>
       <c r="C425" t="inlineStr">
         <is>
-          <t>f2ctq003</t>
+          <t>f2ctq001</t>
         </is>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>f2ctq004</t>
+          <t>f2ctq002</t>
         </is>
       </c>
       <c r="B426" t="inlineStr"/>
       <c r="C426" t="inlineStr">
         <is>
-          <t>f2ctq004</t>
+          <t>f2ctq002</t>
         </is>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>f2ctq005</t>
+          <t>f2ctq003</t>
         </is>
       </c>
       <c r="B427" t="inlineStr"/>
       <c r="C427" t="inlineStr">
         <is>
-          <t>f2ctq005</t>
+          <t>f2ctq003</t>
         </is>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>f2ctq006</t>
+          <t>f2ctq004</t>
         </is>
       </c>
       <c r="B428" t="inlineStr"/>
       <c r="C428" t="inlineStr">
         <is>
-          <t>f2ctq006</t>
+          <t>f2ctq004</t>
         </is>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>f2ctq007</t>
+          <t>f2ctq005</t>
         </is>
       </c>
       <c r="B429" t="inlineStr"/>
       <c r="C429" t="inlineStr">
         <is>
-          <t>f2ctq007</t>
+          <t>f2ctq005</t>
         </is>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>f2ctq008</t>
+          <t>f2ctq006</t>
         </is>
       </c>
       <c r="B430" t="inlineStr"/>
       <c r="C430" t="inlineStr">
         <is>
-          <t>f2ctq008</t>
+          <t>f2ctq006</t>
         </is>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>f2ctq009</t>
+          <t>f2ctq007</t>
         </is>
       </c>
       <c r="B431" t="inlineStr"/>
       <c r="C431" t="inlineStr">
         <is>
-          <t>f2ctq009</t>
+          <t>f2ctq007</t>
         </is>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>f2ctq010</t>
+          <t>f2ctq008</t>
         </is>
       </c>
       <c r="B432" t="inlineStr"/>
       <c r="C432" t="inlineStr">
         <is>
-          <t>f2ctq010</t>
+          <t>f2ctq008</t>
         </is>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>f2ctq011</t>
+          <t>f2ctq009</t>
         </is>
       </c>
       <c r="B433" t="inlineStr"/>
       <c r="C433" t="inlineStr">
         <is>
-          <t>f2ctq011</t>
+          <t>f2ctq009</t>
         </is>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>f2ctq012</t>
+          <t>f2ctq010</t>
         </is>
       </c>
       <c r="B434" t="inlineStr"/>
       <c r="C434" t="inlineStr">
         <is>
-          <t>f2ctq012</t>
+          <t>f2ctq010</t>
         </is>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>f2ctq013</t>
+          <t>f2ctq011</t>
         </is>
       </c>
       <c r="B435" t="inlineStr"/>
       <c r="C435" t="inlineStr">
         <is>
-          <t>f2ctq013</t>
+          <t>f2ctq011</t>
         </is>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>f2ctq014</t>
+          <t>f2ctq012</t>
         </is>
       </c>
       <c r="B436" t="inlineStr"/>
       <c r="C436" t="inlineStr">
         <is>
-          <t>f2ctq014</t>
+          <t>f2ctq012</t>
         </is>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>f2ctq015</t>
+          <t>f2ctq013</t>
         </is>
       </c>
       <c r="B437" t="inlineStr"/>
       <c r="C437" t="inlineStr">
         <is>
-          <t>f2ctq015</t>
+          <t>f2ctq013</t>
         </is>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>f2ctq016</t>
+          <t>f2ctq014</t>
         </is>
       </c>
       <c r="B438" t="inlineStr"/>
       <c r="C438" t="inlineStr">
         <is>
-          <t>f2ctq016</t>
+          <t>f2ctq014</t>
         </is>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>f2ctq017</t>
+          <t>f2ctq015</t>
         </is>
       </c>
       <c r="B439" t="inlineStr"/>
       <c r="C439" t="inlineStr">
         <is>
-          <t>f2ctq017</t>
+          <t>f2ctq015</t>
         </is>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>f2ctq018</t>
+          <t>f2ctq016</t>
         </is>
       </c>
       <c r="B440" t="inlineStr"/>
       <c r="C440" t="inlineStr">
         <is>
-          <t>f2ctq018</t>
+          <t>f2ctq016</t>
         </is>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>f2ctq019</t>
+          <t>f2ctq017</t>
         </is>
       </c>
       <c r="B441" t="inlineStr"/>
       <c r="C441" t="inlineStr">
         <is>
-          <t>f2ctq019</t>
+          <t>f2ctq017</t>
         </is>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>f2ctq020</t>
+          <t>f2ctq018</t>
         </is>
       </c>
       <c r="B442" t="inlineStr"/>
       <c r="C442" t="inlineStr">
         <is>
-          <t>f2ctq020</t>
+          <t>f2ctq018</t>
         </is>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>f2ctq021</t>
+          <t>f2ctq019</t>
         </is>
       </c>
       <c r="B443" t="inlineStr"/>
       <c r="C443" t="inlineStr">
         <is>
-          <t>f2ctq021</t>
+          <t>f2ctq019</t>
         </is>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>f2ctq022</t>
+          <t>f2ctq020</t>
         </is>
       </c>
       <c r="B444" t="inlineStr"/>
       <c r="C444" t="inlineStr">
         <is>
-          <t>f2ctq022</t>
+          <t>f2ctq020</t>
         </is>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>f2ctq023</t>
+          <t>f2ctq021</t>
         </is>
       </c>
       <c r="B445" t="inlineStr"/>
       <c r="C445" t="inlineStr">
         <is>
-          <t>f2ctq023</t>
+          <t>f2ctq021</t>
         </is>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>f2ctq024</t>
+          <t>f2ctq022</t>
         </is>
       </c>
       <c r="B446" t="inlineStr"/>
       <c r="C446" t="inlineStr">
         <is>
-          <t>f2ctq024</t>
+          <t>f2ctq022</t>
         </is>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>formulario_2c_complete</t>
+          <t>f2ctq023</t>
         </is>
       </c>
       <c r="B447" t="inlineStr"/>
       <c r="C447" t="inlineStr">
         <is>
-          <t>formulario_2c_complete</t>
+          <t>f2ctq023</t>
         </is>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>datosepa</t>
+          <t>f2ctq024</t>
         </is>
       </c>
       <c r="B448" t="inlineStr"/>
       <c r="C448" t="inlineStr">
         <is>
-          <t>datosepa</t>
+          <t>f2ctq024</t>
         </is>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>datosepe</t>
+          <t>formulario_2c_complete</t>
         </is>
       </c>
       <c r="B449" t="inlineStr"/>
       <c r="C449" t="inlineStr">
         <is>
-          <t>datosepe</t>
+          <t>formulario_2c_complete</t>
         </is>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>datosep01</t>
+          <t>datosepa</t>
         </is>
       </c>
       <c r="B450" t="inlineStr"/>
       <c r="C450" t="inlineStr">
         <is>
-          <t>datosep01</t>
+          <t>datosepa</t>
         </is>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>datosep02</t>
+          <t>datosepe</t>
         </is>
       </c>
       <c r="B451" t="inlineStr"/>
       <c r="C451" t="inlineStr">
         <is>
-          <t>datosep02</t>
+          <t>datosepe</t>
         </is>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>datosep03</t>
+          <t>datosep01</t>
         </is>
       </c>
       <c r="B452" t="inlineStr"/>
       <c r="C452" t="inlineStr">
         <is>
-          <t>datosep03</t>
+          <t>datosep01</t>
         </is>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>datosep031</t>
+          <t>datosep02</t>
         </is>
       </c>
       <c r="B453" t="inlineStr"/>
       <c r="C453" t="inlineStr">
         <is>
-          <t>datosep031</t>
+          <t>datosep02</t>
         </is>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>datosep04</t>
+          <t>datosep03</t>
         </is>
       </c>
       <c r="B454" t="inlineStr"/>
       <c r="C454" t="inlineStr">
         <is>
-          <t>datosep04</t>
+          <t>datosep03</t>
         </is>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>datosep05</t>
+          <t>datosep031</t>
         </is>
       </c>
       <c r="B455" t="inlineStr"/>
       <c r="C455" t="inlineStr">
         <is>
-          <t>datosep05</t>
+          <t>datosep031</t>
         </is>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>datosep06</t>
+          <t>datosep04</t>
         </is>
       </c>
       <c r="B456" t="inlineStr"/>
       <c r="C456" t="inlineStr">
         <is>
-          <t>datosep06</t>
+          <t>datosep04</t>
         </is>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>datosep15</t>
+          <t>datosep05</t>
         </is>
       </c>
       <c r="B457" t="inlineStr"/>
       <c r="C457" t="inlineStr">
         <is>
-          <t>datosep15</t>
+          <t>datosep05</t>
         </is>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>datosep07</t>
+          <t>datosep06</t>
         </is>
       </c>
       <c r="B458" t="inlineStr"/>
       <c r="C458" t="inlineStr">
         <is>
-          <t>datosep07</t>
+          <t>datosep06</t>
         </is>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>datosep071</t>
+          <t>datosep15</t>
         </is>
       </c>
       <c r="B459" t="inlineStr"/>
       <c r="C459" t="inlineStr">
         <is>
-          <t>datosep071</t>
+          <t>datosep15</t>
         </is>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>datosep08</t>
+          <t>datosep07</t>
         </is>
       </c>
       <c r="B460" t="inlineStr"/>
       <c r="C460" t="inlineStr">
         <is>
-          <t>datosep08</t>
+          <t>datosep07</t>
         </is>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>datosep09</t>
+          <t>datosep071</t>
         </is>
       </c>
       <c r="B461" t="inlineStr"/>
       <c r="C461" t="inlineStr">
         <is>
-          <t>datosep09</t>
+          <t>datosep071</t>
         </is>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>datosep10</t>
+          <t>datosep08</t>
         </is>
       </c>
       <c r="B462" t="inlineStr"/>
       <c r="C462" t="inlineStr">
         <is>
-          <t>datosep10</t>
+          <t>datosep08</t>
         </is>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>datosep16</t>
+          <t>datosep09</t>
         </is>
       </c>
       <c r="B463" t="inlineStr"/>
       <c r="C463" t="inlineStr">
         <is>
-          <t>datosep16</t>
+          <t>datosep09</t>
         </is>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>datosep10a</t>
+          <t>datosep10</t>
         </is>
       </c>
       <c r="B464" t="inlineStr"/>
       <c r="C464" t="inlineStr">
         <is>
-          <t>datosep10a</t>
+          <t>datosep10</t>
         </is>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>datosep11</t>
+          <t>datosep16</t>
         </is>
       </c>
       <c r="B465" t="inlineStr"/>
       <c r="C465" t="inlineStr">
         <is>
-          <t>datosep11</t>
+          <t>datosep16</t>
         </is>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>datosep111</t>
+          <t>datosep10a</t>
         </is>
       </c>
       <c r="B466" t="inlineStr"/>
       <c r="C466" t="inlineStr">
         <is>
-          <t>datosep111</t>
+          <t>datosep10a</t>
         </is>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>datosep12</t>
+          <t>datosep11</t>
         </is>
       </c>
       <c r="B467" t="inlineStr"/>
       <c r="C467" t="inlineStr">
         <is>
-          <t>datosep12</t>
+          <t>datosep11</t>
         </is>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>datosep13</t>
+          <t>datosep111</t>
         </is>
       </c>
       <c r="B468" t="inlineStr"/>
       <c r="C468" t="inlineStr">
         <is>
-          <t>datosep13</t>
+          <t>datosep111</t>
         </is>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>datosep14</t>
+          <t>datosep12</t>
         </is>
       </c>
       <c r="B469" t="inlineStr"/>
       <c r="C469" t="inlineStr">
         <is>
-          <t>datosep14</t>
+          <t>datosep12</t>
         </is>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>datosep21</t>
+          <t>datosep13</t>
         </is>
       </c>
       <c r="B470" t="inlineStr"/>
       <c r="C470" t="inlineStr">
         <is>
-          <t>datosep21</t>
+          <t>datosep13</t>
         </is>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>datosep22</t>
+          <t>datosep14</t>
         </is>
       </c>
       <c r="B471" t="inlineStr"/>
       <c r="C471" t="inlineStr">
         <is>
-          <t>datosep22</t>
+          <t>datosep14</t>
         </is>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>datosep224</t>
+          <t>datosep21</t>
         </is>
       </c>
       <c r="B472" t="inlineStr"/>
       <c r="C472" t="inlineStr">
         <is>
-          <t>datosep224</t>
+          <t>datosep21</t>
         </is>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>datosep23</t>
+          <t>datosep22</t>
         </is>
       </c>
       <c r="B473" t="inlineStr"/>
       <c r="C473" t="inlineStr">
         <is>
-          <t>datosep23</t>
+          <t>datosep22</t>
         </is>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>datosep24</t>
+          <t>datosep224</t>
         </is>
       </c>
       <c r="B474" t="inlineStr"/>
       <c r="C474" t="inlineStr">
         <is>
-          <t>datosep24</t>
+          <t>datosep224</t>
         </is>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>datosep25</t>
+          <t>datosep23</t>
         </is>
       </c>
       <c r="B475" t="inlineStr"/>
       <c r="C475" t="inlineStr">
         <is>
-          <t>datosep25</t>
+          <t>datosep23</t>
         </is>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>datosep26</t>
+          <t>datosep24</t>
         </is>
       </c>
       <c r="B476" t="inlineStr"/>
       <c r="C476" t="inlineStr">
         <is>
-          <t>datosep26</t>
+          <t>datosep24</t>
         </is>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>datosep27</t>
+          <t>datosep25</t>
         </is>
       </c>
       <c r="B477" t="inlineStr"/>
       <c r="C477" t="inlineStr">
         <is>
-          <t>datosep27</t>
+          <t>datosep25</t>
         </is>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>datosep28</t>
+          <t>datosep26</t>
         </is>
       </c>
       <c r="B478" t="inlineStr"/>
       <c r="C478" t="inlineStr">
         <is>
-          <t>datosep28</t>
+          <t>datosep26</t>
         </is>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="inlineStr">
         <is>
-          <t>datosep29</t>
+          <t>datosep27</t>
         </is>
       </c>
       <c r="B479" t="inlineStr"/>
       <c r="C479" t="inlineStr">
         <is>
-          <t>datosep29</t>
+          <t>datosep27</t>
         </is>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>datosep30</t>
+          <t>datosep28</t>
         </is>
       </c>
       <c r="B480" t="inlineStr"/>
       <c r="C480" t="inlineStr">
         <is>
-          <t>datosep30</t>
+          <t>datosep28</t>
         </is>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t>datosep31</t>
+          <t>datosep29</t>
         </is>
       </c>
       <c r="B481" t="inlineStr"/>
       <c r="C481" t="inlineStr">
         <is>
-          <t>datosep31</t>
+          <t>datosep29</t>
         </is>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t>datosep32</t>
+          <t>datosep30</t>
         </is>
       </c>
       <c r="B482" t="inlineStr"/>
       <c r="C482" t="inlineStr">
         <is>
-          <t>datosep32</t>
+          <t>datosep30</t>
         </is>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="inlineStr">
         <is>
-          <t>datosep33</t>
+          <t>datosep31</t>
         </is>
       </c>
       <c r="B483" t="inlineStr"/>
       <c r="C483" t="inlineStr">
         <is>
-          <t>datosep33</t>
+          <t>datosep31</t>
         </is>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="inlineStr">
         <is>
-          <t>datosep34</t>
+          <t>datosep32</t>
         </is>
       </c>
       <c r="B484" t="inlineStr"/>
       <c r="C484" t="inlineStr">
         <is>
-          <t>datosep34</t>
+          <t>datosep32</t>
         </is>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="inlineStr">
         <is>
-          <t>datosep341</t>
+          <t>datosep33</t>
         </is>
       </c>
       <c r="B485" t="inlineStr"/>
       <c r="C485" t="inlineStr">
         <is>
-          <t>datosep341</t>
+          <t>datosep33</t>
         </is>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t>datosep35</t>
+          <t>datosep34</t>
         </is>
       </c>
       <c r="B486" t="inlineStr"/>
       <c r="C486" t="inlineStr">
         <is>
-          <t>datosep35</t>
+          <t>datosep34</t>
         </is>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="inlineStr">
         <is>
-          <t>datosep36</t>
+          <t>datosep341</t>
         </is>
       </c>
       <c r="B487" t="inlineStr"/>
       <c r="C487" t="inlineStr">
         <is>
-          <t>datosep36</t>
+          <t>datosep341</t>
         </is>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="inlineStr">
         <is>
-          <t>datosep37</t>
+          <t>datosep35</t>
         </is>
       </c>
       <c r="B488" t="inlineStr"/>
       <c r="C488" t="inlineStr">
         <is>
-          <t>datosep37</t>
+          <t>datosep35</t>
         </is>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>datosep38</t>
+          <t>datosep36</t>
         </is>
       </c>
       <c r="B489" t="inlineStr"/>
       <c r="C489" t="inlineStr">
         <is>
-          <t>datosep38</t>
+          <t>datosep36</t>
         </is>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="inlineStr">
         <is>
-          <t>datosep39</t>
+          <t>datosep37</t>
         </is>
       </c>
       <c r="B490" t="inlineStr"/>
       <c r="C490" t="inlineStr">
         <is>
-          <t>datosep39</t>
+          <t>datosep37</t>
         </is>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="inlineStr">
         <is>
-          <t>datosep40</t>
+          <t>datosep38</t>
         </is>
       </c>
       <c r="B491" t="inlineStr"/>
       <c r="C491" t="inlineStr">
         <is>
-          <t>datosep40</t>
+          <t>datosep38</t>
         </is>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="inlineStr">
         <is>
-          <t>datosep41</t>
+          <t>datosep39</t>
         </is>
       </c>
       <c r="B492" t="inlineStr"/>
       <c r="C492" t="inlineStr">
         <is>
-          <t>datosep41</t>
+          <t>datosep39</t>
         </is>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="inlineStr">
         <is>
-          <t>datosep42</t>
+          <t>datosep40</t>
         </is>
       </c>
       <c r="B493" t="inlineStr"/>
       <c r="C493" t="inlineStr">
         <is>
-          <t>datosep42</t>
+          <t>datosep40</t>
         </is>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="inlineStr">
         <is>
-          <t>datosep43</t>
+          <t>datosep41</t>
         </is>
       </c>
       <c r="B494" t="inlineStr"/>
       <c r="C494" t="inlineStr">
         <is>
-          <t>datosep43</t>
+          <t>datosep41</t>
         </is>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="inlineStr">
         <is>
-          <t>datosep44</t>
+          <t>datosep42</t>
         </is>
       </c>
       <c r="B495" t="inlineStr"/>
       <c r="C495" t="inlineStr">
         <is>
-          <t>datosep44</t>
+          <t>datosep42</t>
         </is>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="inlineStr">
         <is>
-          <t>datosep442</t>
+          <t>datosep43</t>
         </is>
       </c>
       <c r="B496" t="inlineStr"/>
       <c r="C496" t="inlineStr">
         <is>
-          <t>datosep442</t>
+          <t>datosep43</t>
         </is>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="inlineStr">
         <is>
-          <t>datosep45</t>
+          <t>datosep44</t>
         </is>
       </c>
       <c r="B497" t="inlineStr"/>
       <c r="C497" t="inlineStr">
         <is>
-          <t>datosep45</t>
+          <t>datosep44</t>
         </is>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>thycaf301</t>
+          <t>datosep442</t>
         </is>
       </c>
       <c r="B498" t="inlineStr"/>
       <c r="C498" t="inlineStr">
         <is>
-          <t>thycaf301</t>
+          <t>datosep442</t>
         </is>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="inlineStr">
         <is>
-          <t>thycaf302</t>
+          <t>datosep45</t>
         </is>
       </c>
       <c r="B499" t="inlineStr"/>
       <c r="C499" t="inlineStr">
         <is>
-          <t>thycaf302</t>
+          <t>datosep45</t>
         </is>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="inlineStr">
         <is>
-          <t>thycaf303</t>
+          <t>thycaf301</t>
         </is>
       </c>
       <c r="B500" t="inlineStr"/>
       <c r="C500" t="inlineStr">
         <is>
-          <t>thycaf303</t>
+          <t>thycaf301</t>
         </is>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="inlineStr">
         <is>
-          <t>thycaf304</t>
+          <t>thycaf302</t>
         </is>
       </c>
       <c r="B501" t="inlineStr"/>
       <c r="C501" t="inlineStr">
         <is>
-          <t>thycaf304</t>
+          <t>thycaf302</t>
         </is>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="inlineStr">
         <is>
-          <t>thycaf305</t>
+          <t>thycaf303</t>
         </is>
       </c>
       <c r="B502" t="inlineStr"/>
       <c r="C502" t="inlineStr">
         <is>
-          <t>thycaf305</t>
+          <t>thycaf303</t>
         </is>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="inlineStr">
         <is>
-          <t>thycaf307</t>
+          <t>thycaf304</t>
         </is>
       </c>
       <c r="B503" t="inlineStr"/>
       <c r="C503" t="inlineStr">
         <is>
-          <t>thycaf307</t>
+          <t>thycaf304</t>
         </is>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="inlineStr">
         <is>
-          <t>thycaf308</t>
+          <t>thycaf305</t>
         </is>
       </c>
       <c r="B504" t="inlineStr"/>
       <c r="C504" t="inlineStr">
         <is>
-          <t>thycaf308</t>
+          <t>thycaf305</t>
         </is>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="inlineStr">
         <is>
-          <t>thycaf309</t>
+          <t>thycaf307</t>
         </is>
       </c>
       <c r="B505" t="inlineStr"/>
       <c r="C505" t="inlineStr">
         <is>
-          <t>thycaf309</t>
+          <t>thycaf307</t>
         </is>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="inlineStr">
         <is>
-          <t>thycaf310</t>
+          <t>thycaf308</t>
         </is>
       </c>
       <c r="B506" t="inlineStr"/>
       <c r="C506" t="inlineStr">
         <is>
-          <t>thycaf310</t>
+          <t>thycaf308</t>
         </is>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="inlineStr">
         <is>
-          <t>thycaf311</t>
+          <t>thycaf309</t>
         </is>
       </c>
       <c r="B507" t="inlineStr"/>
       <c r="C507" t="inlineStr">
         <is>
-          <t>thycaf311</t>
+          <t>thycaf309</t>
         </is>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="inlineStr">
         <is>
-          <t>thycaf312</t>
+          <t>thycaf310</t>
         </is>
       </c>
       <c r="B508" t="inlineStr"/>
       <c r="C508" t="inlineStr">
         <is>
-          <t>thycaf312</t>
+          <t>thycaf310</t>
         </is>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="inlineStr">
         <is>
-          <t>thycaf313</t>
+          <t>thycaf311</t>
         </is>
       </c>
       <c r="B509" t="inlineStr"/>
       <c r="C509" t="inlineStr">
         <is>
-          <t>thycaf313</t>
+          <t>thycaf311</t>
         </is>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="inlineStr">
         <is>
-          <t>thycaf314</t>
+          <t>thycaf312</t>
         </is>
       </c>
       <c r="B510" t="inlineStr"/>
       <c r="C510" t="inlineStr">
         <is>
-          <t>thycaf314</t>
+          <t>thycaf312</t>
         </is>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="inlineStr">
         <is>
-          <t>thycaf315</t>
+          <t>thycaf313</t>
         </is>
       </c>
       <c r="B511" t="inlineStr"/>
       <c r="C511" t="inlineStr">
         <is>
-          <t>thycaf315</t>
+          <t>thycaf313</t>
         </is>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="inlineStr">
         <is>
-          <t>thycaf316</t>
+          <t>thycaf314</t>
         </is>
       </c>
       <c r="B512" t="inlineStr"/>
       <c r="C512" t="inlineStr">
         <is>
-          <t>thycaf316</t>
+          <t>thycaf314</t>
         </is>
       </c>
     </row>
     <row r="513">
       <c r="A513" t="inlineStr">
         <is>
-          <t>thycaf317</t>
+          <t>thycaf315</t>
         </is>
       </c>
       <c r="B513" t="inlineStr"/>
       <c r="C513" t="inlineStr">
         <is>
-          <t>thycaf317</t>
+          <t>thycaf315</t>
         </is>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="inlineStr">
         <is>
-          <t>thycaf318</t>
+          <t>thycaf316</t>
         </is>
       </c>
       <c r="B514" t="inlineStr"/>
       <c r="C514" t="inlineStr">
         <is>
-          <t>thycaf318</t>
+          <t>thycaf316</t>
         </is>
       </c>
     </row>
     <row r="515">
       <c r="A515" t="inlineStr">
         <is>
-          <t>thycaf319</t>
+          <t>thycaf317</t>
         </is>
       </c>
       <c r="B515" t="inlineStr"/>
       <c r="C515" t="inlineStr">
         <is>
-          <t>thycaf319</t>
+          <t>thycaf317</t>
         </is>
       </c>
     </row>
     <row r="516">
       <c r="A516" t="inlineStr">
         <is>
-          <t>thycaf320</t>
+          <t>thycaf318</t>
         </is>
       </c>
       <c r="B516" t="inlineStr"/>
       <c r="C516" t="inlineStr">
         <is>
-          <t>thycaf320</t>
+          <t>thycaf318</t>
         </is>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="inlineStr">
         <is>
-          <t>thycaf321</t>
+          <t>thycaf319</t>
         </is>
       </c>
       <c r="B517" t="inlineStr"/>
       <c r="C517" t="inlineStr">
         <is>
-          <t>thycaf321</t>
+          <t>thycaf319</t>
         </is>
       </c>
     </row>
     <row r="518">
       <c r="A518" t="inlineStr">
         <is>
-          <t>thycaf322</t>
+          <t>thycaf320</t>
         </is>
       </c>
       <c r="B518" t="inlineStr"/>
       <c r="C518" t="inlineStr">
         <is>
-          <t>thycaf322</t>
+          <t>thycaf320</t>
         </is>
       </c>
     </row>
     <row r="519">
       <c r="A519" t="inlineStr">
         <is>
-          <t>thycaf323</t>
+          <t>thycaf321</t>
         </is>
       </c>
       <c r="B519" t="inlineStr"/>
       <c r="C519" t="inlineStr">
         <is>
-          <t>thycaf323</t>
+          <t>thycaf321</t>
         </is>
       </c>
     </row>
     <row r="520">
       <c r="A520" t="inlineStr">
         <is>
-          <t>thycaf324</t>
+          <t>thycaf322</t>
         </is>
       </c>
       <c r="B520" t="inlineStr"/>
       <c r="C520" t="inlineStr">
         <is>
-          <t>thycaf324</t>
+          <t>thycaf322</t>
         </is>
       </c>
     </row>
     <row r="521">
       <c r="A521" t="inlineStr">
         <is>
-          <t>datosep69</t>
+          <t>thycaf323</t>
         </is>
       </c>
       <c r="B521" t="inlineStr"/>
       <c r="C521" t="inlineStr">
         <is>
-          <t>datosep69</t>
+          <t>thycaf323</t>
         </is>
       </c>
     </row>
     <row r="522">
       <c r="A522" t="inlineStr">
         <is>
-          <t>datosep70</t>
+          <t>thycaf324</t>
         </is>
       </c>
       <c r="B522" t="inlineStr"/>
       <c r="C522" t="inlineStr">
         <is>
-          <t>datosep70</t>
+          <t>thycaf324</t>
         </is>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="inlineStr">
         <is>
-          <t>datosep71</t>
+          <t>datosep69</t>
         </is>
       </c>
       <c r="B523" t="inlineStr"/>
       <c r="C523" t="inlineStr">
         <is>
-          <t>datosep71</t>
+          <t>datosep69</t>
         </is>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="inlineStr">
         <is>
-          <t>datosep72</t>
-        </is>
-      </c>
-      <c r="B524" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>datosep70</t>
+        </is>
+      </c>
+      <c r="B524" t="inlineStr"/>
       <c r="C524" t="inlineStr">
         <is>
-          <t>datosep72___1</t>
+          <t>datosep70</t>
         </is>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="inlineStr">
         <is>
-          <t>datosep72</t>
-        </is>
-      </c>
-      <c r="B525" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>datosep71</t>
+        </is>
+      </c>
+      <c r="B525" t="inlineStr"/>
       <c r="C525" t="inlineStr">
         <is>
-          <t>datosep72___2</t>
+          <t>datosep71</t>
         </is>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="inlineStr">
         <is>
-          <t>datosep73</t>
-        </is>
-      </c>
-      <c r="B526" t="inlineStr"/>
+          <t>datosep72</t>
+        </is>
+      </c>
+      <c r="B526" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="C526" t="inlineStr">
         <is>
-          <t>datosep73</t>
+          <t>datosep72___1</t>
         </is>
       </c>
     </row>
     <row r="527">
       <c r="A527" t="inlineStr">
         <is>
-          <t>datosep74</t>
-        </is>
-      </c>
-      <c r="B527" t="inlineStr"/>
+          <t>datosep72</t>
+        </is>
+      </c>
+      <c r="B527" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="C527" t="inlineStr">
         <is>
-          <t>datosep74</t>
+          <t>datosep72___2</t>
         </is>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="inlineStr">
         <is>
-          <t>datosep75</t>
+          <t>datosep73</t>
         </is>
       </c>
       <c r="B528" t="inlineStr"/>
       <c r="C528" t="inlineStr">
         <is>
-          <t>datosep75</t>
+          <t>datosep73</t>
         </is>
       </c>
     </row>
     <row r="529">
       <c r="A529" t="inlineStr">
         <is>
-          <t>datosep76</t>
+          <t>datosep74</t>
         </is>
       </c>
       <c r="B529" t="inlineStr"/>
       <c r="C529" t="inlineStr">
         <is>
-          <t>datosep76</t>
+          <t>datosep74</t>
         </is>
       </c>
     </row>
     <row r="530">
       <c r="A530" t="inlineStr">
         <is>
-          <t>datosep77</t>
-        </is>
-      </c>
-      <c r="B530" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>datosep75</t>
+        </is>
+      </c>
+      <c r="B530" t="inlineStr"/>
       <c r="C530" t="inlineStr">
         <is>
-          <t>datosep77___1</t>
+          <t>datosep75</t>
         </is>
       </c>
     </row>
     <row r="531">
       <c r="A531" t="inlineStr">
         <is>
-          <t>datosep77</t>
-        </is>
-      </c>
-      <c r="B531" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>datosep76</t>
+        </is>
+      </c>
+      <c r="B531" t="inlineStr"/>
       <c r="C531" t="inlineStr">
         <is>
-          <t>datosep77___2</t>
+          <t>datosep76</t>
         </is>
       </c>
     </row>
@@ -7871,12 +7871,12 @@
       </c>
       <c r="B532" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C532" t="inlineStr">
         <is>
-          <t>datosep77___3</t>
+          <t>datosep77___1</t>
         </is>
       </c>
     </row>
@@ -7888,12 +7888,12 @@
       </c>
       <c r="B533" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C533" t="inlineStr">
         <is>
-          <t>datosep77___4</t>
+          <t>datosep77___2</t>
         </is>
       </c>
     </row>
@@ -7905,12 +7905,12 @@
       </c>
       <c r="B534" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C534" t="inlineStr">
         <is>
-          <t>datosep77___5</t>
+          <t>datosep77___3</t>
         </is>
       </c>
     </row>
@@ -7922,12 +7922,12 @@
       </c>
       <c r="B535" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C535" t="inlineStr">
         <is>
-          <t>datosep77___6</t>
+          <t>datosep77___4</t>
         </is>
       </c>
     </row>
@@ -7939,202 +7939,202 @@
       </c>
       <c r="B536" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C536" t="inlineStr">
         <is>
-          <t>datosep77___7</t>
+          <t>datosep77___5</t>
         </is>
       </c>
     </row>
     <row r="537">
       <c r="A537" t="inlineStr">
         <is>
-          <t>datosep78</t>
-        </is>
-      </c>
-      <c r="B537" t="inlineStr"/>
+          <t>datosep77</t>
+        </is>
+      </c>
+      <c r="B537" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="C537" t="inlineStr">
         <is>
-          <t>datosep78</t>
+          <t>datosep77___6</t>
         </is>
       </c>
     </row>
     <row r="538">
       <c r="A538" t="inlineStr">
         <is>
-          <t>datosep79</t>
-        </is>
-      </c>
-      <c r="B538" t="inlineStr"/>
+          <t>datosep77</t>
+        </is>
+      </c>
+      <c r="B538" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="C538" t="inlineStr">
         <is>
-          <t>datosep79</t>
+          <t>datosep77___7</t>
         </is>
       </c>
     </row>
     <row r="539">
       <c r="A539" t="inlineStr">
         <is>
-          <t>datosep80</t>
+          <t>datosep78</t>
         </is>
       </c>
       <c r="B539" t="inlineStr"/>
       <c r="C539" t="inlineStr">
         <is>
-          <t>datosep80</t>
+          <t>datosep78</t>
         </is>
       </c>
     </row>
     <row r="540">
       <c r="A540" t="inlineStr">
         <is>
-          <t>datosep81</t>
+          <t>datosep79</t>
         </is>
       </c>
       <c r="B540" t="inlineStr"/>
       <c r="C540" t="inlineStr">
         <is>
-          <t>datosep81</t>
+          <t>datosep79</t>
         </is>
       </c>
     </row>
     <row r="541">
       <c r="A541" t="inlineStr">
         <is>
-          <t>datosep82</t>
+          <t>datosep80</t>
         </is>
       </c>
       <c r="B541" t="inlineStr"/>
       <c r="C541" t="inlineStr">
         <is>
-          <t>datosep82</t>
+          <t>datosep80</t>
         </is>
       </c>
     </row>
     <row r="542">
       <c r="A542" t="inlineStr">
         <is>
-          <t>datosep83</t>
+          <t>datosep81</t>
         </is>
       </c>
       <c r="B542" t="inlineStr"/>
       <c r="C542" t="inlineStr">
         <is>
-          <t>datosep83</t>
+          <t>datosep81</t>
         </is>
       </c>
     </row>
     <row r="543">
       <c r="A543" t="inlineStr">
         <is>
-          <t>datosep84</t>
+          <t>datosep82</t>
         </is>
       </c>
       <c r="B543" t="inlineStr"/>
       <c r="C543" t="inlineStr">
         <is>
-          <t>datosep84</t>
+          <t>datosep82</t>
         </is>
       </c>
     </row>
     <row r="544">
       <c r="A544" t="inlineStr">
         <is>
-          <t>datosep85</t>
+          <t>datosep83</t>
         </is>
       </c>
       <c r="B544" t="inlineStr"/>
       <c r="C544" t="inlineStr">
         <is>
-          <t>datosep85</t>
+          <t>datosep83</t>
         </is>
       </c>
     </row>
     <row r="545">
       <c r="A545" t="inlineStr">
         <is>
-          <t>datosep86</t>
+          <t>datosep84</t>
         </is>
       </c>
       <c r="B545" t="inlineStr"/>
       <c r="C545" t="inlineStr">
         <is>
-          <t>datosep86</t>
+          <t>datosep84</t>
         </is>
       </c>
     </row>
     <row r="546">
       <c r="A546" t="inlineStr">
         <is>
-          <t>datosep87</t>
+          <t>datosep85</t>
         </is>
       </c>
       <c r="B546" t="inlineStr"/>
       <c r="C546" t="inlineStr">
         <is>
-          <t>datosep87</t>
+          <t>datosep85</t>
         </is>
       </c>
     </row>
     <row r="547">
       <c r="A547" t="inlineStr">
         <is>
-          <t>datosep88</t>
+          <t>datosep86</t>
         </is>
       </c>
       <c r="B547" t="inlineStr"/>
       <c r="C547" t="inlineStr">
         <is>
-          <t>datosep88</t>
+          <t>datosep86</t>
         </is>
       </c>
     </row>
     <row r="548">
       <c r="A548" t="inlineStr">
         <is>
-          <t>datosep89</t>
+          <t>datosep87</t>
         </is>
       </c>
       <c r="B548" t="inlineStr"/>
       <c r="C548" t="inlineStr">
         <is>
-          <t>datosep89</t>
+          <t>datosep87</t>
         </is>
       </c>
     </row>
     <row r="549">
       <c r="A549" t="inlineStr">
         <is>
-          <t>datosep90</t>
-        </is>
-      </c>
-      <c r="B549" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>datosep88</t>
+        </is>
+      </c>
+      <c r="B549" t="inlineStr"/>
       <c r="C549" t="inlineStr">
         <is>
-          <t>datosep90___1</t>
+          <t>datosep88</t>
         </is>
       </c>
     </row>
     <row r="550">
       <c r="A550" t="inlineStr">
         <is>
-          <t>datosep90</t>
-        </is>
-      </c>
-      <c r="B550" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>datosep89</t>
+        </is>
+      </c>
+      <c r="B550" t="inlineStr"/>
       <c r="C550" t="inlineStr">
         <is>
-          <t>datosep90___2</t>
+          <t>datosep89</t>
         </is>
       </c>
     </row>
@@ -8146,12 +8146,12 @@
       </c>
       <c r="B551" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C551" t="inlineStr">
         <is>
-          <t>datosep90___3</t>
+          <t>datosep90___1</t>
         </is>
       </c>
     </row>
@@ -8163,1102 +8163,1435 @@
       </c>
       <c r="B552" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C552" t="inlineStr">
         <is>
-          <t>datosep90___4</t>
+          <t>datosep90___2</t>
         </is>
       </c>
     </row>
     <row r="553">
       <c r="A553" t="inlineStr">
         <is>
-          <t>datosep91</t>
-        </is>
-      </c>
-      <c r="B553" t="inlineStr"/>
+          <t>datosep90</t>
+        </is>
+      </c>
+      <c r="B553" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="C553" t="inlineStr">
         <is>
-          <t>datosep91</t>
+          <t>datosep90___3</t>
         </is>
       </c>
     </row>
     <row r="554">
       <c r="A554" t="inlineStr">
         <is>
-          <t>datosep92</t>
-        </is>
-      </c>
-      <c r="B554" t="inlineStr"/>
+          <t>datosep90</t>
+        </is>
+      </c>
+      <c r="B554" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="C554" t="inlineStr">
         <is>
-          <t>datosep92</t>
+          <t>datosep90___4</t>
         </is>
       </c>
     </row>
     <row r="555">
       <c r="A555" t="inlineStr">
         <is>
-          <t>datosep93</t>
+          <t>datosep91</t>
         </is>
       </c>
       <c r="B555" t="inlineStr"/>
       <c r="C555" t="inlineStr">
         <is>
-          <t>datosep93</t>
+          <t>datosep91</t>
         </is>
       </c>
     </row>
     <row r="556">
       <c r="A556" t="inlineStr">
         <is>
-          <t>datosep94</t>
+          <t>datosep92</t>
         </is>
       </c>
       <c r="B556" t="inlineStr"/>
       <c r="C556" t="inlineStr">
         <is>
-          <t>datosep94</t>
+          <t>datosep92</t>
         </is>
       </c>
     </row>
     <row r="557">
       <c r="A557" t="inlineStr">
         <is>
-          <t>datosep95</t>
+          <t>datosep93</t>
         </is>
       </c>
       <c r="B557" t="inlineStr"/>
       <c r="C557" t="inlineStr">
         <is>
-          <t>datosep95</t>
+          <t>datosep93</t>
         </is>
       </c>
     </row>
     <row r="558">
       <c r="A558" t="inlineStr">
         <is>
-          <t>datosep96</t>
+          <t>datosep94</t>
         </is>
       </c>
       <c r="B558" t="inlineStr"/>
       <c r="C558" t="inlineStr">
         <is>
-          <t>datosep96</t>
+          <t>datosep94</t>
         </is>
       </c>
     </row>
     <row r="559">
       <c r="A559" t="inlineStr">
         <is>
-          <t>datosep97</t>
+          <t>datosep95</t>
         </is>
       </c>
       <c r="B559" t="inlineStr"/>
       <c r="C559" t="inlineStr">
         <is>
-          <t>datosep97</t>
+          <t>datosep95</t>
         </is>
       </c>
     </row>
     <row r="560">
       <c r="A560" t="inlineStr">
         <is>
-          <t>datosep98</t>
+          <t>datosep96</t>
         </is>
       </c>
       <c r="B560" t="inlineStr"/>
       <c r="C560" t="inlineStr">
         <is>
-          <t>datosep98</t>
+          <t>datosep96</t>
         </is>
       </c>
     </row>
     <row r="561">
       <c r="A561" t="inlineStr">
         <is>
-          <t>datosep99</t>
+          <t>datosep97</t>
         </is>
       </c>
       <c r="B561" t="inlineStr"/>
       <c r="C561" t="inlineStr">
         <is>
-          <t>datosep99</t>
+          <t>datosep97</t>
         </is>
       </c>
     </row>
     <row r="562">
       <c r="A562" t="inlineStr">
         <is>
-          <t>datosep100</t>
+          <t>datosep98</t>
         </is>
       </c>
       <c r="B562" t="inlineStr"/>
       <c r="C562" t="inlineStr">
         <is>
-          <t>datosep100</t>
+          <t>datosep98</t>
         </is>
       </c>
     </row>
     <row r="563">
       <c r="A563" t="inlineStr">
         <is>
-          <t>datosep101</t>
+          <t>datosep99</t>
         </is>
       </c>
       <c r="B563" t="inlineStr"/>
       <c r="C563" t="inlineStr">
         <is>
-          <t>datosep101</t>
+          <t>datosep99</t>
         </is>
       </c>
     </row>
     <row r="564">
       <c r="A564" t="inlineStr">
         <is>
-          <t>datosep102</t>
+          <t>datosep100</t>
         </is>
       </c>
       <c r="B564" t="inlineStr"/>
       <c r="C564" t="inlineStr">
         <is>
-          <t>datosep102</t>
+          <t>datosep100</t>
         </is>
       </c>
     </row>
     <row r="565">
       <c r="A565" t="inlineStr">
         <is>
-          <t>datosep103</t>
+          <t>datosep101</t>
         </is>
       </c>
       <c r="B565" t="inlineStr"/>
       <c r="C565" t="inlineStr">
         <is>
-          <t>datosep103</t>
+          <t>datosep101</t>
         </is>
       </c>
     </row>
     <row r="566">
       <c r="A566" t="inlineStr">
         <is>
-          <t>datosep104</t>
+          <t>datosep102</t>
         </is>
       </c>
       <c r="B566" t="inlineStr"/>
       <c r="C566" t="inlineStr">
         <is>
-          <t>datosep104</t>
+          <t>datosep102</t>
         </is>
       </c>
     </row>
     <row r="567">
       <c r="A567" t="inlineStr">
         <is>
-          <t>datosep105</t>
+          <t>datosep103</t>
         </is>
       </c>
       <c r="B567" t="inlineStr"/>
       <c r="C567" t="inlineStr">
         <is>
-          <t>datosep105</t>
+          <t>datosep103</t>
         </is>
       </c>
     </row>
     <row r="568">
       <c r="A568" t="inlineStr">
         <is>
-          <t>datosep106</t>
+          <t>datosep104</t>
         </is>
       </c>
       <c r="B568" t="inlineStr"/>
       <c r="C568" t="inlineStr">
         <is>
-          <t>datosep106</t>
+          <t>datosep104</t>
         </is>
       </c>
     </row>
     <row r="569">
       <c r="A569" t="inlineStr">
         <is>
-          <t>datorecu</t>
+          <t>datosep105</t>
         </is>
       </c>
       <c r="B569" t="inlineStr"/>
       <c r="C569" t="inlineStr">
         <is>
-          <t>datorecu</t>
+          <t>datosep105</t>
         </is>
       </c>
     </row>
     <row r="570">
       <c r="A570" t="inlineStr">
         <is>
-          <t>formulario_3_seguimiento_complete</t>
+          <t>datosep106</t>
         </is>
       </c>
       <c r="B570" t="inlineStr"/>
       <c r="C570" t="inlineStr">
         <is>
-          <t>formulario_3_seguimiento_complete</t>
+          <t>datosep106</t>
         </is>
       </c>
     </row>
     <row r="571">
       <c r="A571" t="inlineStr">
         <is>
-          <t>f4_fec_eval</t>
+          <t>datorecu</t>
         </is>
       </c>
       <c r="B571" t="inlineStr"/>
       <c r="C571" t="inlineStr">
         <is>
-          <t>f4_fec_eval</t>
+          <t>datorecu</t>
         </is>
       </c>
     </row>
     <row r="572">
       <c r="A572" t="inlineStr">
         <is>
-          <t>f4_tiedescir</t>
+          <t>formulario_3_seguimiento_complete</t>
         </is>
       </c>
       <c r="B572" t="inlineStr"/>
       <c r="C572" t="inlineStr">
         <is>
-          <t>f4_tiedescir</t>
+          <t>formulario_3_seguimiento_complete</t>
         </is>
       </c>
     </row>
     <row r="573">
       <c r="A573" t="inlineStr">
         <is>
-          <t>f4_tirserdos</t>
+          <t>f4_fec_eval</t>
         </is>
       </c>
       <c r="B573" t="inlineStr"/>
       <c r="C573" t="inlineStr">
         <is>
-          <t>f4_tirserdos</t>
+          <t>f4_fec_eval</t>
         </is>
       </c>
     </row>
     <row r="574">
       <c r="A574" t="inlineStr">
         <is>
-          <t>tiroglobulina_s_rica_ng_ml</t>
+          <t>f4_tiedescir</t>
         </is>
       </c>
       <c r="B574" t="inlineStr"/>
       <c r="C574" t="inlineStr">
         <is>
-          <t>tiroglobulina_s_rica_ng_ml</t>
+          <t>f4_tiedescir</t>
         </is>
       </c>
     </row>
     <row r="575">
       <c r="A575" t="inlineStr">
         <is>
-          <t>metodolog_a_de_tiroglobuli</t>
+          <t>f4_tirserdos</t>
         </is>
       </c>
       <c r="B575" t="inlineStr"/>
       <c r="C575" t="inlineStr">
         <is>
-          <t>metodolog_a_de_tiroglobuli</t>
+          <t>f4_tirserdos</t>
         </is>
       </c>
     </row>
     <row r="576">
       <c r="A576" t="inlineStr">
         <is>
-          <t>sensibilidad_funcional_de</t>
+          <t>tiroglobulina_s_rica_ng_ml</t>
         </is>
       </c>
       <c r="B576" t="inlineStr"/>
       <c r="C576" t="inlineStr">
         <is>
-          <t>sensibilidad_funcional_de</t>
+          <t>tiroglobulina_s_rica_ng_ml</t>
         </is>
       </c>
     </row>
     <row r="577">
       <c r="A577" t="inlineStr">
         <is>
-          <t>anticuerpos_anti_tiroglobu</t>
+          <t>metodolog_a_de_tiroglobuli</t>
         </is>
       </c>
       <c r="B577" t="inlineStr"/>
       <c r="C577" t="inlineStr">
         <is>
-          <t>anticuerpos_anti_tiroglobu</t>
+          <t>metodolog_a_de_tiroglobuli</t>
         </is>
       </c>
     </row>
     <row r="578">
       <c r="A578" t="inlineStr">
         <is>
-          <t>valor_de_anticuerpos_anti</t>
+          <t>sensibilidad_funcional_de</t>
         </is>
       </c>
       <c r="B578" t="inlineStr"/>
       <c r="C578" t="inlineStr">
         <is>
-          <t>valor_de_anticuerpos_anti</t>
+          <t>sensibilidad_funcional_de</t>
         </is>
       </c>
     </row>
     <row r="579">
       <c r="A579" t="inlineStr">
         <is>
-          <t>valor_de_referencia_de_ant</t>
+          <t>anticuerpos_anti_tiroglobu</t>
         </is>
       </c>
       <c r="B579" t="inlineStr"/>
       <c r="C579" t="inlineStr">
         <is>
-          <t>valor_de_referencia_de_ant</t>
+          <t>anticuerpos_anti_tiroglobu</t>
         </is>
       </c>
     </row>
     <row r="580">
       <c r="A580" t="inlineStr">
         <is>
-          <t>tsh_s_rico_micro_ui_ml</t>
+          <t>valor_de_anticuerpos_anti</t>
         </is>
       </c>
       <c r="B580" t="inlineStr"/>
       <c r="C580" t="inlineStr">
         <is>
-          <t>tsh_s_rico_micro_ui_ml</t>
+          <t>valor_de_anticuerpos_anti</t>
         </is>
       </c>
     </row>
     <row r="581">
       <c r="A581" t="inlineStr">
         <is>
-          <t>peso_kg</t>
+          <t>valor_de_referencia_de_ant</t>
         </is>
       </c>
       <c r="B581" t="inlineStr"/>
       <c r="C581" t="inlineStr">
         <is>
-          <t>peso_kg</t>
+          <t>valor_de_referencia_de_ant</t>
         </is>
       </c>
     </row>
     <row r="582">
       <c r="A582" t="inlineStr">
         <is>
-          <t>dosis_de_levotiroxina_mcg</t>
+          <t>tsh_s_rico_micro_ui_ml</t>
         </is>
       </c>
       <c r="B582" t="inlineStr"/>
       <c r="C582" t="inlineStr">
         <is>
-          <t>dosis_de_levotiroxina_mcg</t>
+          <t>tsh_s_rico_micro_ui_ml</t>
         </is>
       </c>
     </row>
     <row r="583">
       <c r="A583" t="inlineStr">
         <is>
-          <t>fecha_de_ecografia_cervica</t>
+          <t>peso_kg</t>
         </is>
       </c>
       <c r="B583" t="inlineStr"/>
       <c r="C583" t="inlineStr">
         <is>
-          <t>fecha_de_ecografia_cervica</t>
+          <t>peso_kg</t>
         </is>
       </c>
     </row>
     <row r="584">
       <c r="A584" t="inlineStr">
         <is>
-          <t>ecografia_cervical</t>
+          <t>dosis_de_levotiroxina_mcg</t>
         </is>
       </c>
       <c r="B584" t="inlineStr"/>
       <c r="C584" t="inlineStr">
         <is>
-          <t>ecografia_cervical</t>
+          <t>dosis_de_levotiroxina_mcg</t>
         </is>
       </c>
     </row>
     <row r="585">
       <c r="A585" t="inlineStr">
         <is>
-          <t>localizaci_n_de_linfonodos</t>
+          <t>fecha_de_ecografia_cervica</t>
         </is>
       </c>
       <c r="B585" t="inlineStr"/>
       <c r="C585" t="inlineStr">
         <is>
-          <t>localizaci_n_de_linfonodos</t>
+          <t>fecha_de_ecografia_cervica</t>
         </is>
       </c>
     </row>
     <row r="586">
       <c r="A586" t="inlineStr">
         <is>
-          <t>f4_localiz_de_linfonodos_sos</t>
+          <t>ecografia_cervical</t>
         </is>
       </c>
       <c r="B586" t="inlineStr"/>
       <c r="C586" t="inlineStr">
         <is>
-          <t>f4_localiz_de_linfonodos_sos</t>
+          <t>ecografia_cervical</t>
         </is>
       </c>
     </row>
     <row r="587">
       <c r="A587" t="inlineStr">
         <is>
-          <t>paaf_de_linfonodos_indeter</t>
+          <t>localizaci_n_de_linfonodos</t>
         </is>
       </c>
       <c r="B587" t="inlineStr"/>
       <c r="C587" t="inlineStr">
         <is>
-          <t>paaf_de_linfonodos_indeter</t>
+          <t>localizaci_n_de_linfonodos</t>
         </is>
       </c>
     </row>
     <row r="588">
       <c r="A588" t="inlineStr">
         <is>
-          <t>dosaje_de_tiroglobulina_en</t>
+          <t>f4_localiz_de_linfonodos_sos</t>
         </is>
       </c>
       <c r="B588" t="inlineStr"/>
       <c r="C588" t="inlineStr">
         <is>
-          <t>dosaje_de_tiroglobulina_en</t>
+          <t>f4_localiz_de_linfonodos_sos</t>
         </is>
       </c>
     </row>
     <row r="589">
       <c r="A589" t="inlineStr">
         <is>
-          <t>valor_de_tiroglobulina_en</t>
+          <t>paaf_de_linfonodos_indeter</t>
         </is>
       </c>
       <c r="B589" t="inlineStr"/>
       <c r="C589" t="inlineStr">
         <is>
-          <t>valor_de_tiroglobulina_en</t>
+          <t>paaf_de_linfonodos_indeter</t>
         </is>
       </c>
     </row>
     <row r="590">
       <c r="A590" t="inlineStr">
         <is>
-          <t>rct_con_baja_dosis_de_i131</t>
+          <t>dosaje_de_tiroglobulina_en</t>
         </is>
       </c>
       <c r="B590" t="inlineStr"/>
       <c r="C590" t="inlineStr">
         <is>
-          <t>rct_con_baja_dosis_de_i131</t>
+          <t>dosaje_de_tiroglobulina_en</t>
         </is>
       </c>
     </row>
     <row r="591">
       <c r="A591" t="inlineStr">
         <is>
-          <t>met_stasis_a_distancia</t>
+          <t>valor_de_tiroglobulina_en</t>
         </is>
       </c>
       <c r="B591" t="inlineStr"/>
       <c r="C591" t="inlineStr">
         <is>
-          <t>met_stasis_a_distancia</t>
+          <t>valor_de_tiroglobulina_en</t>
         </is>
       </c>
     </row>
     <row r="592">
       <c r="A592" t="inlineStr">
         <is>
-          <t>especificar</t>
+          <t>rct_con_baja_dosis_de_i131</t>
         </is>
       </c>
       <c r="B592" t="inlineStr"/>
       <c r="C592" t="inlineStr">
         <is>
-          <t>especificar</t>
+          <t>rct_con_baja_dosis_de_i131</t>
         </is>
       </c>
     </row>
     <row r="593">
       <c r="A593" t="inlineStr">
         <is>
-          <t>estadificaci_n_din_mica_de</t>
+          <t>met_stasis_a_distancia</t>
         </is>
       </c>
       <c r="B593" t="inlineStr"/>
       <c r="C593" t="inlineStr">
         <is>
-          <t>estadificaci_n_din_mica_de</t>
+          <t>met_stasis_a_distancia</t>
         </is>
       </c>
     </row>
     <row r="594">
       <c r="A594" t="inlineStr">
         <is>
-          <t>conductas</t>
+          <t>especificar</t>
         </is>
       </c>
       <c r="B594" t="inlineStr"/>
       <c r="C594" t="inlineStr">
         <is>
-          <t>conductas</t>
+          <t>especificar</t>
         </is>
       </c>
     </row>
     <row r="595">
       <c r="A595" t="inlineStr">
         <is>
-          <t>p_rdida_de_seguimiento_cl</t>
+          <t>estadificaci_n_din_mica_de</t>
         </is>
       </c>
       <c r="B595" t="inlineStr"/>
       <c r="C595" t="inlineStr">
         <is>
-          <t>p_rdida_de_seguimiento_cl</t>
+          <t>estadificaci_n_din_mica_de</t>
         </is>
       </c>
     </row>
     <row r="596">
       <c r="A596" t="inlineStr">
         <is>
-          <t>persistencia_tumoral_prese</t>
+          <t>conductas</t>
         </is>
       </c>
       <c r="B596" t="inlineStr"/>
       <c r="C596" t="inlineStr">
         <is>
-          <t>persistencia_tumoral_prese</t>
+          <t>conductas</t>
         </is>
       </c>
     </row>
     <row r="597">
       <c r="A597" t="inlineStr">
         <is>
-          <t>local_de_persistencia_tumo</t>
+          <t>p_rdida_de_seguimiento_cl</t>
         </is>
       </c>
       <c r="B597" t="inlineStr"/>
       <c r="C597" t="inlineStr">
         <is>
-          <t>local_de_persistencia_tumo</t>
+          <t>p_rdida_de_seguimiento_cl</t>
         </is>
       </c>
     </row>
     <row r="598">
       <c r="A598" t="inlineStr">
         <is>
-          <t>especificar1</t>
+          <t>persistencia_tumoral_prese</t>
         </is>
       </c>
       <c r="B598" t="inlineStr"/>
       <c r="C598" t="inlineStr">
         <is>
-          <t>especificar1</t>
+          <t>persistencia_tumoral_prese</t>
         </is>
       </c>
     </row>
     <row r="599">
       <c r="A599" t="inlineStr">
         <is>
-          <t>conduta_de_la_persistencia</t>
+          <t>local_de_persistencia_tumo</t>
         </is>
       </c>
       <c r="B599" t="inlineStr"/>
       <c r="C599" t="inlineStr">
         <is>
-          <t>conduta_de_la_persistencia</t>
+          <t>local_de_persistencia_tumo</t>
         </is>
       </c>
     </row>
     <row r="600">
       <c r="A600" t="inlineStr">
         <is>
-          <t>recurrencia_reaparici_n_de</t>
+          <t>especificar1</t>
         </is>
       </c>
       <c r="B600" t="inlineStr"/>
       <c r="C600" t="inlineStr">
         <is>
-          <t>recurrencia_reaparici_n_de</t>
+          <t>especificar1</t>
         </is>
       </c>
     </row>
     <row r="601">
       <c r="A601" t="inlineStr">
         <is>
-          <t>fecha_de_recurrencia</t>
+          <t>conduta_de_la_persistencia</t>
         </is>
       </c>
       <c r="B601" t="inlineStr"/>
       <c r="C601" t="inlineStr">
         <is>
-          <t>fecha_de_recurrencia</t>
+          <t>conduta_de_la_persistencia</t>
         </is>
       </c>
     </row>
     <row r="602">
       <c r="A602" t="inlineStr">
         <is>
-          <t>tiempo_de_recurrencia</t>
+          <t>recurrencia_reaparici_n_de</t>
         </is>
       </c>
       <c r="B602" t="inlineStr"/>
       <c r="C602" t="inlineStr">
         <is>
-          <t>tiempo_de_recurrencia</t>
+          <t>recurrencia_reaparici_n_de</t>
         </is>
       </c>
     </row>
     <row r="603">
       <c r="A603" t="inlineStr">
         <is>
-          <t>local_derecurrencia</t>
+          <t>fecha_de_recurrencia</t>
         </is>
       </c>
       <c r="B603" t="inlineStr"/>
       <c r="C603" t="inlineStr">
         <is>
-          <t>local_derecurrencia</t>
+          <t>fecha_de_recurrencia</t>
         </is>
       </c>
     </row>
     <row r="604">
       <c r="A604" t="inlineStr">
         <is>
-          <t>conduta_de_la_recurrencia</t>
+          <t>tiempo_de_recurrencia</t>
         </is>
       </c>
       <c r="B604" t="inlineStr"/>
       <c r="C604" t="inlineStr">
         <is>
-          <t>conduta_de_la_recurrencia</t>
+          <t>tiempo_de_recurrencia</t>
         </is>
       </c>
     </row>
     <row r="605">
       <c r="A605" t="inlineStr">
         <is>
-          <t>muerte_relacionada_a_ct</t>
+          <t>local_derecurrencia</t>
         </is>
       </c>
       <c r="B605" t="inlineStr"/>
       <c r="C605" t="inlineStr">
         <is>
-          <t>muerte_relacionada_a_ct</t>
+          <t>local_derecurrencia</t>
         </is>
       </c>
     </row>
     <row r="606">
       <c r="A606" t="inlineStr">
         <is>
-          <t>muerte_por_otra_causa_no_r</t>
+          <t>conduta_de_la_recurrencia</t>
         </is>
       </c>
       <c r="B606" t="inlineStr"/>
       <c r="C606" t="inlineStr">
         <is>
-          <t>muerte_por_otra_causa_no_r</t>
+          <t>conduta_de_la_recurrencia</t>
         </is>
       </c>
     </row>
     <row r="607">
       <c r="A607" t="inlineStr">
         <is>
-          <t>causa_de_muerte</t>
+          <t>muerte_relacionada_a_ct</t>
         </is>
       </c>
       <c r="B607" t="inlineStr"/>
       <c r="C607" t="inlineStr">
         <is>
-          <t>causa_de_muerte</t>
+          <t>muerte_relacionada_a_ct</t>
         </is>
       </c>
     </row>
     <row r="608">
       <c r="A608" t="inlineStr">
         <is>
-          <t>fecha_de_muerte</t>
+          <t>muerte_por_otra_causa_no_r</t>
         </is>
       </c>
       <c r="B608" t="inlineStr"/>
       <c r="C608" t="inlineStr">
         <is>
-          <t>fecha_de_muerte</t>
+          <t>muerte_por_otra_causa_no_r</t>
         </is>
       </c>
     </row>
     <row r="609">
       <c r="A609" t="inlineStr">
         <is>
-          <t>tratamientos_adicionales</t>
+          <t>causa_de_muerte</t>
         </is>
       </c>
       <c r="B609" t="inlineStr"/>
       <c r="C609" t="inlineStr">
         <is>
-          <t>tratamientos_adicionales</t>
+          <t>causa_de_muerte</t>
         </is>
       </c>
     </row>
     <row r="610">
       <c r="A610" t="inlineStr">
         <is>
-          <t>formulario_4_seguimiento_complete</t>
+          <t>fecha_de_muerte</t>
         </is>
       </c>
       <c r="B610" t="inlineStr"/>
       <c r="C610" t="inlineStr">
         <is>
-          <t>formulario_4_seguimiento_complete</t>
+          <t>fecha_de_muerte</t>
         </is>
       </c>
     </row>
     <row r="611">
       <c r="A611" t="inlineStr">
         <is>
-          <t>f5_ciradi</t>
+          <t>tratamientos_adicionales</t>
         </is>
       </c>
       <c r="B611" t="inlineStr"/>
       <c r="C611" t="inlineStr">
         <is>
-          <t>f5_ciradi</t>
+          <t>tratamientos_adicionales</t>
         </is>
       </c>
     </row>
     <row r="612">
       <c r="A612" t="inlineStr">
         <is>
-          <t>f5_fecciradi</t>
+          <t>f4tq001</t>
         </is>
       </c>
       <c r="B612" t="inlineStr"/>
       <c r="C612" t="inlineStr">
         <is>
-          <t>f5_fecciradi</t>
+          <t>f4tq001</t>
         </is>
       </c>
     </row>
     <row r="613">
       <c r="A613" t="inlineStr">
         <is>
-          <t>f5_loccir</t>
+          <t>f4tq002</t>
         </is>
       </c>
       <c r="B613" t="inlineStr"/>
       <c r="C613" t="inlineStr">
         <is>
-          <t>f5_loccir</t>
+          <t>f4tq002</t>
         </is>
       </c>
     </row>
     <row r="614">
       <c r="A614" t="inlineStr">
         <is>
-          <t>f5_loccir05</t>
+          <t>f4tq003</t>
         </is>
       </c>
       <c r="B614" t="inlineStr"/>
       <c r="C614" t="inlineStr">
         <is>
-          <t>f5_loccir05</t>
+          <t>f4tq003</t>
         </is>
       </c>
     </row>
     <row r="615">
       <c r="A615" t="inlineStr">
         <is>
-          <t>f5_tipcircer</t>
+          <t>f4tq004</t>
         </is>
       </c>
       <c r="B615" t="inlineStr"/>
       <c r="C615" t="inlineStr">
         <is>
-          <t>f5_tipcircer</t>
+          <t>f4tq004</t>
         </is>
       </c>
     </row>
     <row r="616">
       <c r="A616" t="inlineStr">
         <is>
-          <t>f5_analin</t>
+          <t>f4tq005</t>
         </is>
       </c>
       <c r="B616" t="inlineStr"/>
       <c r="C616" t="inlineStr">
         <is>
-          <t>f5_analin</t>
+          <t>f4tq005</t>
         </is>
       </c>
     </row>
     <row r="617">
       <c r="A617" t="inlineStr">
         <is>
-          <t>f5_numtotlinret</t>
+          <t>f4tq006</t>
         </is>
       </c>
       <c r="B617" t="inlineStr"/>
       <c r="C617" t="inlineStr">
         <is>
-          <t>f5_numtotlinret</t>
+          <t>f4tq006</t>
         </is>
       </c>
     </row>
     <row r="618">
       <c r="A618" t="inlineStr">
         <is>
-          <t>f5_numtotlinposmal</t>
+          <t>f4tq007</t>
         </is>
       </c>
       <c r="B618" t="inlineStr"/>
       <c r="C618" t="inlineStr">
         <is>
-          <t>f5_numtotlinposmal</t>
+          <t>f4tq007</t>
         </is>
       </c>
     </row>
     <row r="619">
       <c r="A619" t="inlineStr">
         <is>
-          <t>f5_tammaylinpos</t>
+          <t>f4tq008</t>
         </is>
       </c>
       <c r="B619" t="inlineStr"/>
       <c r="C619" t="inlineStr">
         <is>
-          <t>f5_tammaylinpos</t>
+          <t>f4tq008</t>
         </is>
       </c>
     </row>
     <row r="620">
       <c r="A620" t="inlineStr">
         <is>
-          <t>f5_iodradadi</t>
+          <t>f4tq009</t>
         </is>
       </c>
       <c r="B620" t="inlineStr"/>
       <c r="C620" t="inlineStr">
         <is>
-          <t>f5_iodradadi</t>
+          <t>f4tq009</t>
         </is>
       </c>
     </row>
     <row r="621">
       <c r="A621" t="inlineStr">
         <is>
-          <t>f5_dosiodrad</t>
+          <t>f4tq010</t>
         </is>
       </c>
       <c r="B621" t="inlineStr"/>
       <c r="C621" t="inlineStr">
         <is>
-          <t>f5_dosiodrad</t>
+          <t>f4tq010</t>
         </is>
       </c>
     </row>
     <row r="622">
       <c r="A622" t="inlineStr">
         <is>
-          <t>f5_feciodadi</t>
+          <t>f4tq011</t>
         </is>
       </c>
       <c r="B622" t="inlineStr"/>
       <c r="C622" t="inlineStr">
         <is>
-          <t>f5_feciodadi</t>
+          <t>f4tq011</t>
         </is>
       </c>
     </row>
     <row r="623">
       <c r="A623" t="inlineStr">
         <is>
-          <t>f5_rctdosadidei131</t>
+          <t>f4tq012</t>
         </is>
       </c>
       <c r="B623" t="inlineStr"/>
       <c r="C623" t="inlineStr">
         <is>
-          <t>f5_rctdosadidei131</t>
+          <t>f4tq012</t>
         </is>
       </c>
     </row>
     <row r="624">
       <c r="A624" t="inlineStr">
         <is>
-          <t>f5_metdis</t>
+          <t>f4tq013</t>
         </is>
       </c>
       <c r="B624" t="inlineStr"/>
       <c r="C624" t="inlineStr">
         <is>
-          <t>f5_metdis</t>
+          <t>f4tq013</t>
         </is>
       </c>
     </row>
     <row r="625">
       <c r="A625" t="inlineStr">
         <is>
-          <t>f5_metdis03</t>
+          <t>f4tq014</t>
         </is>
       </c>
       <c r="B625" t="inlineStr"/>
       <c r="C625" t="inlineStr">
         <is>
-          <t>f5_metdis03</t>
+          <t>f4tq014</t>
         </is>
       </c>
     </row>
     <row r="626">
       <c r="A626" t="inlineStr">
         <is>
-          <t>f5_eveadviod</t>
+          <t>f4tq015</t>
         </is>
       </c>
       <c r="B626" t="inlineStr"/>
       <c r="C626" t="inlineStr">
         <is>
-          <t>f5_eveadviod</t>
+          <t>f4tq015</t>
         </is>
       </c>
     </row>
     <row r="627">
       <c r="A627" t="inlineStr">
         <is>
-          <t>f5_eveadviod01</t>
+          <t>f4tq016</t>
         </is>
       </c>
       <c r="B627" t="inlineStr"/>
       <c r="C627" t="inlineStr">
         <is>
-          <t>f5_eveadviod01</t>
+          <t>f4tq016</t>
         </is>
       </c>
     </row>
     <row r="628">
       <c r="A628" t="inlineStr">
         <is>
-          <t>f5_usotki</t>
+          <t>f4tq017</t>
         </is>
       </c>
       <c r="B628" t="inlineStr"/>
       <c r="C628" t="inlineStr">
         <is>
-          <t>f5_usotki</t>
+          <t>f4tq017</t>
         </is>
       </c>
     </row>
     <row r="629">
       <c r="A629" t="inlineStr">
         <is>
-          <t>f5_usotki01</t>
+          <t>f4tq018</t>
         </is>
       </c>
       <c r="B629" t="inlineStr"/>
       <c r="C629" t="inlineStr">
         <is>
-          <t>f5_usotki01</t>
+          <t>f4tq018</t>
         </is>
       </c>
     </row>
     <row r="630">
       <c r="A630" t="inlineStr">
         <is>
-          <t>f5_eveadvusotki</t>
+          <t>f4tq019</t>
         </is>
       </c>
       <c r="B630" t="inlineStr"/>
       <c r="C630" t="inlineStr">
         <is>
-          <t>f5_eveadvusotki</t>
+          <t>f4tq019</t>
         </is>
       </c>
     </row>
     <row r="631">
       <c r="A631" t="inlineStr">
         <is>
-          <t>f5_eveadvusotki01</t>
+          <t>f4tq020</t>
         </is>
       </c>
       <c r="B631" t="inlineStr"/>
       <c r="C631" t="inlineStr">
         <is>
-          <t>f5_eveadvusotki01</t>
+          <t>f4tq020</t>
         </is>
       </c>
     </row>
     <row r="632">
       <c r="A632" t="inlineStr">
         <is>
-          <t>f5_rad</t>
+          <t>f4tq021</t>
         </is>
       </c>
       <c r="B632" t="inlineStr"/>
       <c r="C632" t="inlineStr">
         <is>
-          <t>f5_rad</t>
+          <t>f4tq021</t>
         </is>
       </c>
     </row>
     <row r="633">
       <c r="A633" t="inlineStr">
         <is>
-          <t>f5_locrad</t>
+          <t>f4tq022</t>
         </is>
       </c>
       <c r="B633" t="inlineStr"/>
       <c r="C633" t="inlineStr">
         <is>
-          <t>f5_locrad</t>
+          <t>f4tq022</t>
         </is>
       </c>
     </row>
     <row r="634">
       <c r="A634" t="inlineStr">
         <is>
-          <t>f5_otrteradi</t>
+          <t>f4tq023</t>
         </is>
       </c>
       <c r="B634" t="inlineStr"/>
       <c r="C634" t="inlineStr">
         <is>
-          <t>f5_otrteradi</t>
+          <t>f4tq023</t>
         </is>
       </c>
     </row>
     <row r="635">
       <c r="A635" t="inlineStr">
         <is>
-          <t>f5_otrteradi01</t>
+          <t>formulario_4_seguimiento_complete</t>
         </is>
       </c>
       <c r="B635" t="inlineStr"/>
       <c r="C635" t="inlineStr">
         <is>
-          <t>f5_otrteradi01</t>
+          <t>formulario_4_seguimiento_complete</t>
         </is>
       </c>
     </row>
     <row r="636">
       <c r="A636" t="inlineStr">
         <is>
-          <t>formulario_5_seguimiento_complete</t>
+          <t>f5_ciradi</t>
         </is>
       </c>
       <c r="B636" t="inlineStr"/>
       <c r="C636" t="inlineStr">
+        <is>
+          <t>f5_ciradi</t>
+        </is>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" t="inlineStr">
+        <is>
+          <t>f5_fecciradi</t>
+        </is>
+      </c>
+      <c r="B637" t="inlineStr"/>
+      <c r="C637" t="inlineStr">
+        <is>
+          <t>f5_fecciradi</t>
+        </is>
+      </c>
+    </row>
+    <row r="638">
+      <c r="A638" t="inlineStr">
+        <is>
+          <t>f5_loccir</t>
+        </is>
+      </c>
+      <c r="B638" t="inlineStr"/>
+      <c r="C638" t="inlineStr">
+        <is>
+          <t>f5_loccir</t>
+        </is>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" t="inlineStr">
+        <is>
+          <t>f5_loccir05</t>
+        </is>
+      </c>
+      <c r="B639" t="inlineStr"/>
+      <c r="C639" t="inlineStr">
+        <is>
+          <t>f5_loccir05</t>
+        </is>
+      </c>
+    </row>
+    <row r="640">
+      <c r="A640" t="inlineStr">
+        <is>
+          <t>f5_tipcircer</t>
+        </is>
+      </c>
+      <c r="B640" t="inlineStr"/>
+      <c r="C640" t="inlineStr">
+        <is>
+          <t>f5_tipcircer</t>
+        </is>
+      </c>
+    </row>
+    <row r="641">
+      <c r="A641" t="inlineStr">
+        <is>
+          <t>f5_analin</t>
+        </is>
+      </c>
+      <c r="B641" t="inlineStr"/>
+      <c r="C641" t="inlineStr">
+        <is>
+          <t>f5_analin</t>
+        </is>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642" t="inlineStr">
+        <is>
+          <t>f5_numtotlinret</t>
+        </is>
+      </c>
+      <c r="B642" t="inlineStr"/>
+      <c r="C642" t="inlineStr">
+        <is>
+          <t>f5_numtotlinret</t>
+        </is>
+      </c>
+    </row>
+    <row r="643">
+      <c r="A643" t="inlineStr">
+        <is>
+          <t>f5_numtotlinposmal</t>
+        </is>
+      </c>
+      <c r="B643" t="inlineStr"/>
+      <c r="C643" t="inlineStr">
+        <is>
+          <t>f5_numtotlinposmal</t>
+        </is>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644" t="inlineStr">
+        <is>
+          <t>f5_tammaylinpos</t>
+        </is>
+      </c>
+      <c r="B644" t="inlineStr"/>
+      <c r="C644" t="inlineStr">
+        <is>
+          <t>f5_tammaylinpos</t>
+        </is>
+      </c>
+    </row>
+    <row r="645">
+      <c r="A645" t="inlineStr">
+        <is>
+          <t>f5_iodradadi</t>
+        </is>
+      </c>
+      <c r="B645" t="inlineStr"/>
+      <c r="C645" t="inlineStr">
+        <is>
+          <t>f5_iodradadi</t>
+        </is>
+      </c>
+    </row>
+    <row r="646">
+      <c r="A646" t="inlineStr">
+        <is>
+          <t>f5_dosiodrad</t>
+        </is>
+      </c>
+      <c r="B646" t="inlineStr"/>
+      <c r="C646" t="inlineStr">
+        <is>
+          <t>f5_dosiodrad</t>
+        </is>
+      </c>
+    </row>
+    <row r="647">
+      <c r="A647" t="inlineStr">
+        <is>
+          <t>f5_feciodadi</t>
+        </is>
+      </c>
+      <c r="B647" t="inlineStr"/>
+      <c r="C647" t="inlineStr">
+        <is>
+          <t>f5_feciodadi</t>
+        </is>
+      </c>
+    </row>
+    <row r="648">
+      <c r="A648" t="inlineStr">
+        <is>
+          <t>f5_rctdosadidei131</t>
+        </is>
+      </c>
+      <c r="B648" t="inlineStr"/>
+      <c r="C648" t="inlineStr">
+        <is>
+          <t>f5_rctdosadidei131</t>
+        </is>
+      </c>
+    </row>
+    <row r="649">
+      <c r="A649" t="inlineStr">
+        <is>
+          <t>f5_metdis</t>
+        </is>
+      </c>
+      <c r="B649" t="inlineStr"/>
+      <c r="C649" t="inlineStr">
+        <is>
+          <t>f5_metdis</t>
+        </is>
+      </c>
+    </row>
+    <row r="650">
+      <c r="A650" t="inlineStr">
+        <is>
+          <t>f5_metdis03</t>
+        </is>
+      </c>
+      <c r="B650" t="inlineStr"/>
+      <c r="C650" t="inlineStr">
+        <is>
+          <t>f5_metdis03</t>
+        </is>
+      </c>
+    </row>
+    <row r="651">
+      <c r="A651" t="inlineStr">
+        <is>
+          <t>f5_eveadviod</t>
+        </is>
+      </c>
+      <c r="B651" t="inlineStr"/>
+      <c r="C651" t="inlineStr">
+        <is>
+          <t>f5_eveadviod</t>
+        </is>
+      </c>
+    </row>
+    <row r="652">
+      <c r="A652" t="inlineStr">
+        <is>
+          <t>f5_eveadviod01</t>
+        </is>
+      </c>
+      <c r="B652" t="inlineStr"/>
+      <c r="C652" t="inlineStr">
+        <is>
+          <t>f5_eveadviod01</t>
+        </is>
+      </c>
+    </row>
+    <row r="653">
+      <c r="A653" t="inlineStr">
+        <is>
+          <t>f5_usotki</t>
+        </is>
+      </c>
+      <c r="B653" t="inlineStr"/>
+      <c r="C653" t="inlineStr">
+        <is>
+          <t>f5_usotki</t>
+        </is>
+      </c>
+    </row>
+    <row r="654">
+      <c r="A654" t="inlineStr">
+        <is>
+          <t>f5_usotki01</t>
+        </is>
+      </c>
+      <c r="B654" t="inlineStr"/>
+      <c r="C654" t="inlineStr">
+        <is>
+          <t>f5_usotki01</t>
+        </is>
+      </c>
+    </row>
+    <row r="655">
+      <c r="A655" t="inlineStr">
+        <is>
+          <t>f5_eveadvusotki</t>
+        </is>
+      </c>
+      <c r="B655" t="inlineStr"/>
+      <c r="C655" t="inlineStr">
+        <is>
+          <t>f5_eveadvusotki</t>
+        </is>
+      </c>
+    </row>
+    <row r="656">
+      <c r="A656" t="inlineStr">
+        <is>
+          <t>f5_eveadvusotki01</t>
+        </is>
+      </c>
+      <c r="B656" t="inlineStr"/>
+      <c r="C656" t="inlineStr">
+        <is>
+          <t>f5_eveadvusotki01</t>
+        </is>
+      </c>
+    </row>
+    <row r="657">
+      <c r="A657" t="inlineStr">
+        <is>
+          <t>f5_rad</t>
+        </is>
+      </c>
+      <c r="B657" t="inlineStr"/>
+      <c r="C657" t="inlineStr">
+        <is>
+          <t>f5_rad</t>
+        </is>
+      </c>
+    </row>
+    <row r="658">
+      <c r="A658" t="inlineStr">
+        <is>
+          <t>f5_locrad</t>
+        </is>
+      </c>
+      <c r="B658" t="inlineStr"/>
+      <c r="C658" t="inlineStr">
+        <is>
+          <t>f5_locrad</t>
+        </is>
+      </c>
+    </row>
+    <row r="659">
+      <c r="A659" t="inlineStr">
+        <is>
+          <t>f5_otrteradi</t>
+        </is>
+      </c>
+      <c r="B659" t="inlineStr"/>
+      <c r="C659" t="inlineStr">
+        <is>
+          <t>f5_otrteradi</t>
+        </is>
+      </c>
+    </row>
+    <row r="660">
+      <c r="A660" t="inlineStr">
+        <is>
+          <t>f5_otrteradi01</t>
+        </is>
+      </c>
+      <c r="B660" t="inlineStr"/>
+      <c r="C660" t="inlineStr">
+        <is>
+          <t>f5_otrteradi01</t>
+        </is>
+      </c>
+    </row>
+    <row r="661">
+      <c r="A661" t="inlineStr">
+        <is>
+          <t>formulario_5_seguimiento_complete</t>
+        </is>
+      </c>
+      <c r="B661" t="inlineStr"/>
+      <c r="C661" t="inlineStr">
         <is>
           <t>formulario_5_seguimiento_complete</t>
         </is>
